--- a/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
+++ b/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\anssi\rec-secu-sys-ctrl-acces-phys-videoprot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E985973-5C05-4E66-A2F2-782C137CD8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BE9702-B38E-4C85-BC5B-45003DABF276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="636" windowWidth="19716" windowHeight="12324" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -59,9 +59,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>ANSSI - Sécurisation des systèmes de contrôle d’accès physique et vidéoprotection (v2.2)</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -2155,6 +2152,9 @@
   </si>
   <si>
     <t>[R+] Recommandation renforcée</t>
+  </si>
+  <si>
+    <t>ANSSI - Sécurisation des systèmes de contrôle d’accès physique et vidéoprotection (v2.2) [Recommandations]</t>
   </si>
 </sst>
 </file>
@@ -2588,39 +2588,39 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2642,15 +2642,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -2658,7 +2658,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2674,23 +2674,23 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>696</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2713,13 +2713,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>8</v>
@@ -2728,13 +2728,13 @@
         <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>29</v>
-      </c>
-      <c r="H1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2742,47 +2742,47 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
-        <v>36</v>
-      </c>
       <c r="E4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -2790,271 +2790,271 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
+        <v>493</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="s">
-        <v>494</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
         <v>47</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>495</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E11" t="s">
-        <v>496</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
         <v>50</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>496</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E12" t="s">
-        <v>497</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
         <v>54</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>498</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E14" t="s">
-        <v>499</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
         <v>58</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
+        <v>500</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E16" t="s">
-        <v>501</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" t="s">
         <v>62</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>502</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E18" t="s">
-        <v>503</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
         <v>66</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>504</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E20" t="s">
-        <v>505</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -3062,872 +3062,872 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
         <v>71</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>507</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E23" t="s">
-        <v>508</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
         <v>74</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
+        <v>508</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E24" t="s">
-        <v>509</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="H24" t="s">
         <v>76</v>
-      </c>
-      <c r="H24" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
         <v>78</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>509</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E25" t="s">
-        <v>510</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
         <v>83</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>512</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E28" t="s">
-        <v>513</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="H28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" t="s">
         <v>87</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>514</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E30" t="s">
-        <v>515</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="H30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" t="s">
         <v>90</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>515</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E31" t="s">
-        <v>516</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="H31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" t="s">
         <v>94</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>517</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E33" t="s">
-        <v>518</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="H33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" t="s">
         <v>97</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>518</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E34" t="s">
-        <v>519</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="H34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" t="s">
         <v>102</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
+        <v>521</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E37" t="s">
-        <v>522</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" t="s">
         <v>106</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
+        <v>523</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E39" t="s">
-        <v>524</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="H39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" t="s">
         <v>109</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>524</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E40" t="s">
-        <v>525</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="H40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" t="s">
         <v>112</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
+        <v>525</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E41" t="s">
-        <v>526</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="H41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
         <v>115</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>526</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E42" t="s">
-        <v>527</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="H42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E43" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" t="s">
         <v>119</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
+        <v>528</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E44" t="s">
-        <v>529</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="H44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E45" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" t="s">
         <v>123</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
+        <v>530</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E46" t="s">
-        <v>531</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="H46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" t="s">
         <v>126</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
+        <v>531</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E47" t="s">
-        <v>532</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E48" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" t="s">
         <v>130</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
+        <v>533</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E49" t="s">
-        <v>534</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="H49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" t="s">
         <v>133</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
+        <v>534</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E50" t="s">
-        <v>535</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="H50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E51" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" t="s">
         <v>138</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
+        <v>537</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E53" t="s">
-        <v>538</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="H53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" t="s">
         <v>142</v>
       </c>
-      <c r="D55" t="s">
-        <v>143</v>
-      </c>
       <c r="E55" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E56" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
+        <v>144</v>
+      </c>
+      <c r="D57" t="s">
         <v>145</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
+        <v>541</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E57" t="s">
-        <v>542</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="H57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E58" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D59" t="s">
         <v>149</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
+        <v>543</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E59" t="s">
-        <v>544</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="H59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C60" t="s">
+        <v>151</v>
+      </c>
+      <c r="D60" t="s">
         <v>152</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
+        <v>544</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E60" t="s">
-        <v>545</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="G60" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E62" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63" t="s">
+        <v>156</v>
+      </c>
+      <c r="D63" t="s">
         <v>157</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
+        <v>547</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E63" t="s">
-        <v>548</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="H63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
+        <v>159</v>
+      </c>
+      <c r="D64" t="s">
         <v>160</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
+        <v>548</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E64" t="s">
-        <v>549</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="H64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
+        <v>162</v>
+      </c>
+      <c r="D65" t="s">
         <v>163</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
+        <v>549</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E65" t="s">
-        <v>550</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="G65" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E66" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
+        <v>166</v>
+      </c>
+      <c r="D67" t="s">
         <v>167</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
+        <v>551</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E67" t="s">
-        <v>552</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="H67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C68" t="s">
+        <v>169</v>
+      </c>
+      <c r="D68" t="s">
         <v>170</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
+        <v>552</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E68" t="s">
-        <v>553</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="H68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3935,44 +3935,44 @@
         <v>5</v>
       </c>
       <c r="D69" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E69" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E70" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C71" t="s">
+        <v>174</v>
+      </c>
+      <c r="D71" t="s">
         <v>175</v>
       </c>
-      <c r="D71" t="s">
-        <v>176</v>
-      </c>
       <c r="E71" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3980,587 +3980,587 @@
         <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E72" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E73" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C74" t="s">
+        <v>178</v>
+      </c>
+      <c r="D74" t="s">
         <v>179</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
+        <v>558</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E74" t="s">
-        <v>559</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="G74" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C75" t="s">
+        <v>181</v>
+      </c>
+      <c r="D75" t="s">
         <v>182</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>559</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E75" t="s">
-        <v>560</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="H75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C76" t="s">
+        <v>184</v>
+      </c>
+      <c r="D76" t="s">
         <v>185</v>
       </c>
-      <c r="D76" t="s">
-        <v>186</v>
-      </c>
       <c r="E76" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C77" t="s">
+        <v>186</v>
+      </c>
+      <c r="D77" t="s">
         <v>187</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
+        <v>561</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E77" t="s">
-        <v>562</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="H77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C78" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" t="s">
         <v>190</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
+        <v>562</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E78" t="s">
-        <v>563</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="H78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E79" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C80" t="s">
+        <v>193</v>
+      </c>
+      <c r="D80" t="s">
         <v>194</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
+        <v>564</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E80" t="s">
-        <v>565</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="H80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D81" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E81" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C82" t="s">
+        <v>197</v>
+      </c>
+      <c r="D82" t="s">
         <v>198</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
+        <v>566</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E82" t="s">
-        <v>567</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="H82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C83" t="s">
+        <v>200</v>
+      </c>
+      <c r="D83" t="s">
         <v>201</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E83" t="s">
-        <v>568</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D84" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C85" t="s">
+        <v>204</v>
+      </c>
+      <c r="D85" t="s">
         <v>205</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
+        <v>569</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E85" t="s">
-        <v>570</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="H85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C86" t="s">
+        <v>207</v>
+      </c>
+      <c r="D86" t="s">
         <v>208</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
+        <v>570</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E86" t="s">
-        <v>571</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="H86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C87" t="s">
+        <v>210</v>
+      </c>
+      <c r="D87" t="s">
         <v>211</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
+        <v>571</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E87" t="s">
-        <v>572</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="H87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D88" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C89" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" t="s">
         <v>215</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
+        <v>573</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E89" t="s">
-        <v>574</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="H89" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D90" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E90" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C91" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" t="s">
         <v>219</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>575</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E91" t="s">
-        <v>576</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="H91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C93" t="s">
+        <v>222</v>
+      </c>
+      <c r="D93" t="s">
         <v>223</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
+        <v>577</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E93" t="s">
-        <v>578</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="H93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C94" t="s">
+        <v>225</v>
+      </c>
+      <c r="D94" t="s">
         <v>226</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>578</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E94" t="s">
-        <v>579</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="H94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D95" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E95" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C96" t="s">
+        <v>229</v>
+      </c>
+      <c r="D96" t="s">
         <v>230</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>580</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E96" t="s">
-        <v>581</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="H96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C97" t="s">
+        <v>232</v>
+      </c>
+      <c r="D97" t="s">
         <v>233</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
+        <v>581</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E97" t="s">
-        <v>582</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="H97" t="s">
         <v>235</v>
-      </c>
-      <c r="H97" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C98" t="s">
+        <v>236</v>
+      </c>
+      <c r="D98" t="s">
         <v>237</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>582</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E98" t="s">
-        <v>583</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="G98" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C99" t="s">
+        <v>239</v>
+      </c>
+      <c r="D99" t="s">
         <v>240</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
+        <v>583</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E99" t="s">
-        <v>584</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="H99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C100" t="s">
+        <v>242</v>
+      </c>
+      <c r="D100" t="s">
         <v>243</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>692</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E100" t="s">
-        <v>693</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="H100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C101" t="s">
+        <v>245</v>
+      </c>
+      <c r="D101" t="s">
         <v>246</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
+        <v>584</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E101" t="s">
-        <v>585</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="H101" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
@@ -4568,368 +4568,368 @@
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E102" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D103" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E103" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C104" t="s">
+        <v>250</v>
+      </c>
+      <c r="D104" t="s">
         <v>251</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
+        <v>587</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E104" t="s">
-        <v>588</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="H104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C105" t="s">
+        <v>253</v>
+      </c>
+      <c r="D105" t="s">
         <v>254</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>588</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E105" t="s">
-        <v>589</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="H105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C106" t="s">
+        <v>256</v>
+      </c>
+      <c r="D106" t="s">
         <v>257</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>589</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E106" t="s">
-        <v>590</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="H106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C107" t="s">
+        <v>259</v>
+      </c>
+      <c r="D107" t="s">
         <v>260</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
+        <v>590</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E107" t="s">
-        <v>591</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="H107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C108" t="s">
+        <v>262</v>
+      </c>
+      <c r="D108" t="s">
         <v>263</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
+        <v>591</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E108" t="s">
-        <v>592</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="H108" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C109" t="s">
+        <v>265</v>
+      </c>
+      <c r="D109" t="s">
         <v>266</v>
       </c>
-      <c r="D109" t="s">
-        <v>267</v>
-      </c>
       <c r="E109" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H109" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D110" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E110" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C111" t="s">
+        <v>268</v>
+      </c>
+      <c r="D111" t="s">
         <v>269</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>594</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E111" t="s">
-        <v>595</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="H111" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C112" t="s">
+        <v>271</v>
+      </c>
+      <c r="D112" t="s">
         <v>272</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
+        <v>595</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E112" t="s">
-        <v>596</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="H112" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C113" t="s">
+        <v>274</v>
+      </c>
+      <c r="D113" t="s">
         <v>275</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
+        <v>596</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E113" t="s">
-        <v>597</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="G113" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H113" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C114" t="s">
+        <v>277</v>
+      </c>
+      <c r="D114" t="s">
         <v>278</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
+        <v>597</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E114" t="s">
-        <v>598</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="H114" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C115" t="s">
+        <v>280</v>
+      </c>
+      <c r="D115" t="s">
         <v>281</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
+        <v>598</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E115" t="s">
-        <v>599</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="H115" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C116" t="s">
+        <v>283</v>
+      </c>
+      <c r="D116" t="s">
         <v>284</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
+        <v>599</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E116" t="s">
-        <v>600</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="H116" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C117" t="s">
+        <v>286</v>
+      </c>
+      <c r="D117" t="s">
         <v>287</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
+        <v>600</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E117" t="s">
-        <v>601</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="H117" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D118" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E118" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C119" t="s">
+        <v>290</v>
+      </c>
+      <c r="D119" t="s">
         <v>291</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
+        <v>602</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E119" t="s">
-        <v>603</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="H119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
@@ -4937,135 +4937,135 @@
         <v>5</v>
       </c>
       <c r="D120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C122" t="s">
+        <v>295</v>
+      </c>
+      <c r="D122" t="s">
         <v>296</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
+        <v>605</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E122" t="s">
-        <v>606</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="H122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D123" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E123" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C124" t="s">
+        <v>299</v>
+      </c>
+      <c r="D124" t="s">
         <v>300</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
+        <v>607</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E124" t="s">
-        <v>608</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="H124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E125" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C126" t="s">
+        <v>303</v>
+      </c>
+      <c r="D126" t="s">
         <v>304</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
+        <v>609</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E126" t="s">
-        <v>610</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="H126" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B127" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C127" t="s">
+        <v>306</v>
+      </c>
+      <c r="D127" t="s">
         <v>307</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
+        <v>610</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E127" t="s">
-        <v>611</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="H127" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
@@ -5073,340 +5073,340 @@
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E128" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D129" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E129" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B130" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C130" t="s">
+        <v>311</v>
+      </c>
+      <c r="D130" t="s">
         <v>312</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
+        <v>613</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E130" t="s">
-        <v>614</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="H130" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D131" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E131" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B132" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C132" t="s">
+        <v>315</v>
+      </c>
+      <c r="D132" t="s">
         <v>316</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
+        <v>615</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E132" t="s">
-        <v>616</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="H132" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B133" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C133" t="s">
+        <v>318</v>
+      </c>
+      <c r="D133" t="s">
         <v>319</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
+        <v>616</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E133" t="s">
-        <v>617</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="H133" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D134" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E134" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B135" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C135" t="s">
+        <v>322</v>
+      </c>
+      <c r="D135" t="s">
         <v>323</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
+        <v>618</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E135" t="s">
-        <v>619</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="H135" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B136" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C136" t="s">
+        <v>325</v>
+      </c>
+      <c r="D136" t="s">
         <v>326</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
+        <v>619</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E136" t="s">
-        <v>620</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="H136" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D137" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E137" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B138" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C138" t="s">
+        <v>329</v>
+      </c>
+      <c r="D138" t="s">
         <v>330</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
+        <v>621</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E138" t="s">
-        <v>622</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="H138" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D139" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E139" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C140" t="s">
+        <v>333</v>
+      </c>
+      <c r="D140" t="s">
         <v>334</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
+        <v>623</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E140" t="s">
-        <v>624</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="H140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B141" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C141" t="s">
+        <v>336</v>
+      </c>
+      <c r="D141" t="s">
         <v>337</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
+        <v>624</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E141" t="s">
-        <v>625</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="H141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B142" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C142" t="s">
+        <v>339</v>
+      </c>
+      <c r="D142" t="s">
         <v>340</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
+        <v>625</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E142" t="s">
-        <v>626</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="H142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D143" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E143" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B144" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C144" t="s">
+        <v>343</v>
+      </c>
+      <c r="D144" t="s">
         <v>344</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
+        <v>627</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E144" t="s">
-        <v>628</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="H144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D145" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E145" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B146" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C146" t="s">
+        <v>347</v>
+      </c>
+      <c r="D146" t="s">
         <v>348</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
+        <v>629</v>
+      </c>
+      <c r="F146" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E146" t="s">
-        <v>630</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="H146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
@@ -5414,395 +5414,395 @@
         <v>5</v>
       </c>
       <c r="D147" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E147" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D148" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E148" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C149" t="s">
+        <v>352</v>
+      </c>
+      <c r="D149" t="s">
         <v>353</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
+        <v>632</v>
+      </c>
+      <c r="F149" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E149" t="s">
-        <v>633</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="H149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D150" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E150" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B151" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C151" t="s">
+        <v>356</v>
+      </c>
+      <c r="D151" t="s">
         <v>357</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
+        <v>634</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="E151" t="s">
-        <v>635</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="H151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D152" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E152" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B153" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C153" t="s">
+        <v>360</v>
+      </c>
+      <c r="D153" t="s">
         <v>361</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
+        <v>636</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="E153" t="s">
-        <v>637</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="H153" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B154" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C154" t="s">
+        <v>363</v>
+      </c>
+      <c r="D154" t="s">
         <v>364</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
+        <v>637</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E154" t="s">
-        <v>638</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="H154" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D155" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E155" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D156" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E156" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D157" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E157" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B158" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C158" t="s">
+        <v>369</v>
+      </c>
+      <c r="D158" t="s">
         <v>370</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
+        <v>641</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="E158" t="s">
-        <v>642</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="H158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B159" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C159" t="s">
+        <v>372</v>
+      </c>
+      <c r="D159" t="s">
         <v>373</v>
       </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
+        <v>642</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="E159" t="s">
-        <v>643</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="H159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D160" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E160" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B161" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C161" t="s">
+        <v>376</v>
+      </c>
+      <c r="D161" t="s">
         <v>377</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
+        <v>644</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E161" t="s">
-        <v>645</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="H161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D162" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E162" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D163" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E163" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B164" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C164" t="s">
+        <v>381</v>
+      </c>
+      <c r="D164" t="s">
         <v>382</v>
       </c>
-      <c r="D164" t="s">
-        <v>383</v>
-      </c>
       <c r="E164" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H164" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D165" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E165" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B166" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C166" t="s">
+        <v>384</v>
+      </c>
+      <c r="D166" t="s">
         <v>385</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
+        <v>649</v>
+      </c>
+      <c r="F166" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="E166" t="s">
-        <v>650</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="H166" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E167" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B168" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C168" t="s">
+        <v>388</v>
+      </c>
+      <c r="D168" t="s">
         <v>389</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
+        <v>651</v>
+      </c>
+      <c r="F168" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E168" t="s">
-        <v>652</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="H168" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D169" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E169" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B170" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C170" t="s">
+        <v>392</v>
+      </c>
+      <c r="D170" t="s">
         <v>393</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
+        <v>653</v>
+      </c>
+      <c r="F170" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E170" t="s">
-        <v>654</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="H170" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
@@ -5810,192 +5810,192 @@
         <v>5</v>
       </c>
       <c r="D171" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E171" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E172" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B173" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C173" t="s">
+        <v>397</v>
+      </c>
+      <c r="D173" t="s">
         <v>398</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
+        <v>656</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E173" t="s">
-        <v>657</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="H173" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D174" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E174" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B175" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C175" t="s">
+        <v>401</v>
+      </c>
+      <c r="D175" t="s">
         <v>402</v>
       </c>
-      <c r="D175" t="s">
-        <v>403</v>
-      </c>
       <c r="E175" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H175" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D176" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E176" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B177" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C177" t="s">
+        <v>404</v>
+      </c>
+      <c r="D177" t="s">
         <v>405</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
+        <v>660</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="E177" t="s">
-        <v>661</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="H177" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B178" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C178" t="s">
+        <v>407</v>
+      </c>
+      <c r="D178" t="s">
         <v>408</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
+        <v>661</v>
+      </c>
+      <c r="F178" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="E178" t="s">
-        <v>662</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="H178" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B179" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C179" t="s">
+        <v>410</v>
+      </c>
+      <c r="D179" t="s">
         <v>411</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
+        <v>662</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E179" t="s">
-        <v>663</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="H179" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D180" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E180" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B181" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C181" t="s">
+        <v>414</v>
+      </c>
+      <c r="D181" t="s">
         <v>415</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
+        <v>664</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="E181" t="s">
-        <v>665</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="H181" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
@@ -6003,339 +6003,339 @@
         <v>5</v>
       </c>
       <c r="D182" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E182" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D183" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E183" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B184" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C184" t="s">
+        <v>419</v>
+      </c>
+      <c r="D184" t="s">
         <v>420</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
+        <v>667</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E184" t="s">
-        <v>668</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="H184" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B185" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C185" t="s">
+        <v>422</v>
+      </c>
+      <c r="D185" t="s">
         <v>423</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
+        <v>668</v>
+      </c>
+      <c r="F185" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E185" t="s">
-        <v>669</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="H185" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B186" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C186" t="s">
+        <v>425</v>
+      </c>
+      <c r="D186" t="s">
         <v>426</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
+        <v>669</v>
+      </c>
+      <c r="F186" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E186" t="s">
-        <v>670</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="H186" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D187" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E187" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B188" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C188" t="s">
+        <v>429</v>
+      </c>
+      <c r="D188" t="s">
         <v>430</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
+        <v>671</v>
+      </c>
+      <c r="F188" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E188" t="s">
-        <v>672</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="H188" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E189" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E190" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B191" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C191" t="s">
+        <v>434</v>
+      </c>
+      <c r="D191" t="s">
         <v>435</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
+        <v>674</v>
+      </c>
+      <c r="F191" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E191" t="s">
-        <v>675</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="H191" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D192" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E192" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B193" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C193" t="s">
+        <v>438</v>
+      </c>
+      <c r="D193" t="s">
         <v>439</v>
       </c>
-      <c r="D193" t="s">
-        <v>440</v>
-      </c>
       <c r="E193" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H193" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D194" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E194" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B195" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C195" t="s">
+        <v>441</v>
+      </c>
+      <c r="D195" t="s">
         <v>442</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
+        <v>678</v>
+      </c>
+      <c r="F195" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E195" t="s">
-        <v>679</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="H195" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D196" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E196" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B197" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C197" t="s">
+        <v>445</v>
+      </c>
+      <c r="D197" t="s">
         <v>446</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
+        <v>680</v>
+      </c>
+      <c r="F197" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="E197" t="s">
-        <v>681</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="H197" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D198" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E198" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B199" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C199" t="s">
+        <v>449</v>
+      </c>
+      <c r="D199" t="s">
         <v>450</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
+        <v>682</v>
+      </c>
+      <c r="F199" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="E199" t="s">
-        <v>683</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="H199" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D200" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E200" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B201" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C201" t="s">
+        <v>453</v>
+      </c>
+      <c r="D201" t="s">
         <v>454</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
+        <v>684</v>
+      </c>
+      <c r="F201" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="E201" t="s">
-        <v>685</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="H201" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
@@ -6343,112 +6343,112 @@
         <v>5</v>
       </c>
       <c r="D202" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E202" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D203" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E203" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B204" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C204" t="s">
+        <v>458</v>
+      </c>
+      <c r="D204" t="s">
         <v>459</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
+        <v>687</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="E204" t="s">
-        <v>688</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="H204" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D205" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E205" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B206" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C206" t="s">
+        <v>462</v>
+      </c>
+      <c r="D206" t="s">
         <v>463</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
+        <v>689</v>
+      </c>
+      <c r="F206" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="E206" t="s">
-        <v>690</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="H206" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D207" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E207" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B208" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C208" t="s">
+        <v>466</v>
+      </c>
+      <c r="D208" t="s">
         <v>467</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
+        <v>691</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="E208" t="s">
-        <v>692</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="H208" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -6472,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -6480,7 +6480,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6505,40 +6505,40 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
+++ b/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\anssi\rec-secu-sys-ctrl-acces-phys-videoprot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BE9702-B38E-4C85-BC5B-45003DABF276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0AF98F-EBAB-4246-A1FA-3AF806A060D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="636" windowWidth="19716" windowHeight="12324" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -1557,9 +1557,6 @@
     <t>Identifier les zones avec leurs niveaux de protection attendus</t>
   </si>
   <si>
-    <t>Niveaudesûretédeséquipementsetdesinstallationsdecontrôled'accès physique.</t>
-  </si>
-  <si>
     <t>Identifier les niveaux de sûreté adaptés aux menaces des sites</t>
   </si>
   <si>
@@ -1605,9 +1602,6 @@
     <t>Protéger les liaisons filaires</t>
   </si>
   <si>
-    <t>Connexionsentreles têtes de lecture et l'UTL</t>
-  </si>
-  <si>
     <t>Privilégier des connexions point-à-point entre les têtes de lecture et l'UTL</t>
   </si>
   <si>
@@ -1623,12 +1617,6 @@
     <t>Activer un deuxième chiffrement dans le cas d'une connectivité sans-fil</t>
   </si>
   <si>
-    <t>Réseausupport</t>
-  </si>
-  <si>
-    <t>Segmentationauseinduréseausupport</t>
-  </si>
-  <si>
     <t>Cloisonner logiquement les dispositifs au sein du réseau support</t>
   </si>
   <si>
@@ -1647,33 +1635,21 @@
     <t>Contrôler les accès aux ports réseau par vérification des adresses MAC</t>
   </si>
   <si>
-    <t>Mutualisationdesdispositifsdecontrôled'accèsphysiquesurunmêmeréseau support</t>
-  </si>
-  <si>
     <t>Cloisonner logiquement au sein d'un réseau support les UTL associées à des zones de niveaux de protection attendus distincts</t>
   </si>
   <si>
-    <t>Mutualisation des dispositifs de contrôle d'accès physique et de vidéoprotec- tion sur un même réseau support</t>
-  </si>
-  <si>
     <t>Éviter de mutualiser les dispositifs de contrôle d'accès et de vidéoprotection sur un même réseau support</t>
   </si>
   <si>
     <t>Mettre en place un cloisonnement logique entre les dispositifs de contrôle d'accès et de vidéoprotection mutualisés sur un même réseau support</t>
   </si>
   <si>
-    <t>Réseausupportdescamérasplacéesàl'extérieur de la zone contrôlée</t>
-  </si>
-  <si>
     <t>Dédier physiquement un réseau support pour les caméras extérieures</t>
   </si>
   <si>
     <t>Cloisonner logiquement le réseau des caméras extérieures</t>
   </si>
   <si>
-    <t>Réseaufédérateur</t>
-  </si>
-  <si>
     <t>Filtrage des flux entre les réseaux support</t>
   </si>
   <si>
@@ -1704,9 +1680,6 @@
     <t>Interconnexion</t>
   </si>
   <si>
-    <t>Interconnexionentreunsystèmedecontrôled'accèsphysiqueetleSIdel'entité</t>
-  </si>
-  <si>
     <t>Éviter une interconnexion avec le SI de l'entité</t>
   </si>
   <si>
@@ -1716,9 +1689,6 @@
     <t>Protéger les flux échangés entre le système de contrôle d'accès et le SI de l'entité</t>
   </si>
   <si>
-    <t>Interconnexion entre un système de contrôle d'accès physique et un système devidéoprotection</t>
-  </si>
-  <si>
     <t>Privilégier une solution s'appuyant sur deux centres de gestion distincts</t>
   </si>
   <si>
@@ -1737,9 +1707,6 @@
     <t>Sécurité des éléments support d'un système de contrôle d'accès physique</t>
   </si>
   <si>
-    <t>Badgesursupportphysique</t>
-  </si>
-  <si>
     <t>Ne pas stocker d'informations critiques sur le badge</t>
   </si>
   <si>
@@ -1755,9 +1722,6 @@
     <t>Garantir l'unicité d'un badge</t>
   </si>
   <si>
-    <t>Badgevirtuel sur ordiphone</t>
-  </si>
-  <si>
     <t>Éviter l'usage de badges virtuels sur ordiphone</t>
   </si>
   <si>
@@ -1944,9 +1908,6 @@
     <t>Anticiper la procédure de remplacement de clés cryptographiques en cas de compromission</t>
   </si>
   <si>
-    <t>Chiffrementetauthentificationdesfluxenprovenanceetàdestinationdesdispositifs devidéoprotection</t>
-  </si>
-  <si>
     <t>Privilégier les solutions d'authentification et de chiffrement non propriétaires</t>
   </si>
   <si>
@@ -2142,19 +2103,58 @@
     <t>Configurer des alertes en temps réel</t>
   </si>
   <si>
+    <t>[R] Recommandation à l'état de l'art</t>
+  </si>
+  <si>
+    <t>[R-] Recommandation alternative de premier niveau</t>
+  </si>
+  <si>
+    <t>[R+] Recommandation renforcée</t>
+  </si>
+  <si>
+    <t>ANSSI - Sécurisation des systèmes de contrôle d’accès physique et vidéoprotection (v2.2) [Recommandations]</t>
+  </si>
+  <si>
+    <t>Niveau de sûreté des équipements et des installations de contrôle d'accès physique</t>
+  </si>
+  <si>
+    <t>Connexions entre les têtes de lecture et l'UTL</t>
+  </si>
+  <si>
+    <t>Réseau support</t>
+  </si>
+  <si>
+    <t>Segmentation au sein du réseau support</t>
+  </si>
+  <si>
+    <t>Mutualisation des dispositifs de contrôle d'accès physique sur un même réseau support</t>
+  </si>
+  <si>
+    <t>Mutualisation des dispositifs de contrôle d'accès physique et de vidéoprotection sur un même réseau support</t>
+  </si>
+  <si>
+    <t>Réseau support des caméras placées à l'extérieur de la zone contrôlée</t>
+  </si>
+  <si>
+    <t>Réseau fédérateur</t>
+  </si>
+  <si>
+    <t>Interconnexion entre un système de contrôle d'accès physique et le SI de l'entité</t>
+  </si>
+  <si>
+    <t>Interconnexion entre un système de contrôle d'accès physique et un système de vidéoprotection</t>
+  </si>
+  <si>
+    <t>Badge sur support physique</t>
+  </si>
+  <si>
+    <t>Badge virtuel sur ordiphone</t>
+  </si>
+  <si>
+    <t>Chiffrement et authentification des flux en provenance et à destination des dispositifs de vidéoprotection</t>
+  </si>
+  <si>
     <t>Procéder immédiatement à l'interruption de l'alimentation électrique &amp; déconnexion du réseau support en cas de détection d'une tentative d'intrusion physique sur platine d'interphone ou visiophone IP.</t>
-  </si>
-  <si>
-    <t>[R] Recommandation à l'état de l'art</t>
-  </si>
-  <si>
-    <t>[R-] Recommandation alternative de premier niveau</t>
-  </si>
-  <si>
-    <t>[R+] Recommandation renforcée</t>
-  </si>
-  <si>
-    <t>ANSSI - Sécurisation des systèmes de contrôle d’accès physique et vidéoprotection (v2.2) [Recommandations]</t>
   </si>
 </sst>
 </file>
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
@@ -2674,7 +2674,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -2929,7 +2929,7 @@
         <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>497</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2946,7 +2946,7 @@
         <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>55</v>
@@ -2963,7 +2963,7 @@
         <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -2980,7 +2980,7 @@
         <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>59</v>
@@ -2997,7 +2997,7 @@
         <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3014,7 +3014,7 @@
         <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>63</v>
@@ -3031,7 +3031,7 @@
         <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3048,7 +3048,7 @@
         <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>67</v>
@@ -3065,7 +3065,7 @@
         <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -3076,7 +3076,7 @@
         <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3093,7 +3093,7 @@
         <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>72</v>
@@ -3116,7 +3116,7 @@
         <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>75</v>
@@ -3139,7 +3139,7 @@
         <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>79</v>
@@ -3156,7 +3156,7 @@
         <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -3167,7 +3167,7 @@
         <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3184,7 +3184,7 @@
         <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>84</v>
@@ -3201,7 +3201,7 @@
         <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>513</v>
+        <v>684</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3218,7 +3218,7 @@
         <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>88</v>
@@ -3241,7 +3241,7 @@
         <v>90</v>
       </c>
       <c r="E31" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>91</v>
@@ -3258,7 +3258,7 @@
         <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3275,7 +3275,7 @@
         <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>95</v>
@@ -3298,7 +3298,7 @@
         <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>98</v>
@@ -3315,7 +3315,7 @@
         <v>99</v>
       </c>
       <c r="E35" t="s">
-        <v>519</v>
+        <v>685</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -3326,7 +3326,7 @@
         <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>520</v>
+        <v>686</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3343,7 +3343,7 @@
         <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>103</v>
@@ -3360,7 +3360,7 @@
         <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3377,7 +3377,7 @@
         <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>107</v>
@@ -3400,7 +3400,7 @@
         <v>109</v>
       </c>
       <c r="E40" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>110</v>
@@ -3423,7 +3423,7 @@
         <v>112</v>
       </c>
       <c r="E41" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>113</v>
@@ -3446,7 +3446,7 @@
         <v>115</v>
       </c>
       <c r="E42" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>116</v>
@@ -3463,7 +3463,7 @@
         <v>117</v>
       </c>
       <c r="E43" t="s">
-        <v>527</v>
+        <v>687</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3480,7 +3480,7 @@
         <v>119</v>
       </c>
       <c r="E44" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>120</v>
@@ -3497,7 +3497,7 @@
         <v>121</v>
       </c>
       <c r="E45" t="s">
-        <v>529</v>
+        <v>688</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -3514,7 +3514,7 @@
         <v>123</v>
       </c>
       <c r="E46" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>124</v>
@@ -3537,7 +3537,7 @@
         <v>126</v>
       </c>
       <c r="E47" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>127</v>
@@ -3557,7 +3557,7 @@
         <v>128</v>
       </c>
       <c r="E48" t="s">
-        <v>532</v>
+        <v>689</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3574,7 +3574,7 @@
         <v>130</v>
       </c>
       <c r="E49" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>131</v>
@@ -3597,7 +3597,7 @@
         <v>133</v>
       </c>
       <c r="E50" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>134</v>
@@ -3614,7 +3614,7 @@
         <v>135</v>
       </c>
       <c r="E51" t="s">
-        <v>535</v>
+        <v>690</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -3625,7 +3625,7 @@
         <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3642,7 +3642,7 @@
         <v>138</v>
       </c>
       <c r="E53" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>139</v>
@@ -3659,7 +3659,7 @@
         <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -3676,7 +3676,7 @@
         <v>142</v>
       </c>
       <c r="E55" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>479</v>
@@ -3693,7 +3693,7 @@
         <v>143</v>
       </c>
       <c r="E56" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3710,7 +3710,7 @@
         <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>146</v>
@@ -3727,7 +3727,7 @@
         <v>147</v>
       </c>
       <c r="E58" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -3744,7 +3744,7 @@
         <v>149</v>
       </c>
       <c r="E59" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>150</v>
@@ -3767,7 +3767,7 @@
         <v>152</v>
       </c>
       <c r="E60" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>153</v>
@@ -3787,7 +3787,7 @@
         <v>154</v>
       </c>
       <c r="E61" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -3798,7 +3798,7 @@
         <v>155</v>
       </c>
       <c r="E62" t="s">
-        <v>546</v>
+        <v>691</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -3815,7 +3815,7 @@
         <v>157</v>
       </c>
       <c r="E63" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>158</v>
@@ -3838,7 +3838,7 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>161</v>
@@ -3861,7 +3861,7 @@
         <v>163</v>
       </c>
       <c r="E65" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>164</v>
@@ -3881,7 +3881,7 @@
         <v>165</v>
       </c>
       <c r="E66" t="s">
-        <v>550</v>
+        <v>692</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3898,7 +3898,7 @@
         <v>167</v>
       </c>
       <c r="E67" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>168</v>
@@ -3921,7 +3921,7 @@
         <v>170</v>
       </c>
       <c r="E68" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>171</v>
@@ -3938,7 +3938,7 @@
         <v>172</v>
       </c>
       <c r="E69" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3949,7 +3949,7 @@
         <v>173</v>
       </c>
       <c r="E70" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -3966,7 +3966,7 @@
         <v>175</v>
       </c>
       <c r="E71" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>480</v>
@@ -3983,7 +3983,7 @@
         <v>176</v>
       </c>
       <c r="E72" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -3994,7 +3994,7 @@
         <v>177</v>
       </c>
       <c r="E73" t="s">
-        <v>557</v>
+        <v>693</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -4011,7 +4011,7 @@
         <v>179</v>
       </c>
       <c r="E74" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>180</v>
@@ -4037,7 +4037,7 @@
         <v>182</v>
       </c>
       <c r="E75" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>183</v>
@@ -4060,7 +4060,7 @@
         <v>185</v>
       </c>
       <c r="E76" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>481</v>
@@ -4083,7 +4083,7 @@
         <v>187</v>
       </c>
       <c r="E77" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>188</v>
@@ -4106,7 +4106,7 @@
         <v>190</v>
       </c>
       <c r="E78" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>191</v>
@@ -4123,7 +4123,7 @@
         <v>192</v>
       </c>
       <c r="E79" t="s">
-        <v>563</v>
+        <v>694</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4140,7 +4140,7 @@
         <v>194</v>
       </c>
       <c r="E80" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>195</v>
@@ -4157,7 +4157,7 @@
         <v>196</v>
       </c>
       <c r="E81" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4174,7 +4174,7 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>199</v>
@@ -4197,7 +4197,7 @@
         <v>201</v>
       </c>
       <c r="E83" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>202</v>
@@ -4214,7 +4214,7 @@
         <v>203</v>
       </c>
       <c r="E84" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4231,7 +4231,7 @@
         <v>205</v>
       </c>
       <c r="E85" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>206</v>
@@ -4254,7 +4254,7 @@
         <v>208</v>
       </c>
       <c r="E86" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>209</v>
@@ -4277,7 +4277,7 @@
         <v>211</v>
       </c>
       <c r="E87" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>212</v>
@@ -4294,7 +4294,7 @@
         <v>213</v>
       </c>
       <c r="E88" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -4311,7 +4311,7 @@
         <v>215</v>
       </c>
       <c r="E89" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>216</v>
@@ -4328,7 +4328,7 @@
         <v>217</v>
       </c>
       <c r="E90" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4345,7 +4345,7 @@
         <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>220</v>
@@ -4362,7 +4362,7 @@
         <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4379,7 +4379,7 @@
         <v>223</v>
       </c>
       <c r="E93" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>224</v>
@@ -4402,7 +4402,7 @@
         <v>226</v>
       </c>
       <c r="E94" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>227</v>
@@ -4419,7 +4419,7 @@
         <v>228</v>
       </c>
       <c r="E95" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4436,7 +4436,7 @@
         <v>230</v>
       </c>
       <c r="E96" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>231</v>
@@ -4459,7 +4459,7 @@
         <v>233</v>
       </c>
       <c r="E97" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>234</v>
@@ -4482,7 +4482,7 @@
         <v>237</v>
       </c>
       <c r="E98" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>238</v>
@@ -4508,7 +4508,7 @@
         <v>240</v>
       </c>
       <c r="E99" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>241</v>
@@ -4531,7 +4531,7 @@
         <v>243</v>
       </c>
       <c r="E100" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>244</v>
@@ -4554,7 +4554,7 @@
         <v>246</v>
       </c>
       <c r="E101" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>247</v>
@@ -4571,7 +4571,7 @@
         <v>248</v>
       </c>
       <c r="E102" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -4582,7 +4582,7 @@
         <v>249</v>
       </c>
       <c r="E103" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4599,7 +4599,7 @@
         <v>251</v>
       </c>
       <c r="E104" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>252</v>
@@ -4622,7 +4622,7 @@
         <v>254</v>
       </c>
       <c r="E105" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>255</v>
@@ -4645,7 +4645,7 @@
         <v>257</v>
       </c>
       <c r="E106" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>258</v>
@@ -4668,7 +4668,7 @@
         <v>260</v>
       </c>
       <c r="E107" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>261</v>
@@ -4691,7 +4691,7 @@
         <v>263</v>
       </c>
       <c r="E108" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>264</v>
@@ -4714,7 +4714,7 @@
         <v>266</v>
       </c>
       <c r="E109" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>482</v>
@@ -4731,7 +4731,7 @@
         <v>267</v>
       </c>
       <c r="E110" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4748,7 +4748,7 @@
         <v>269</v>
       </c>
       <c r="E111" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>270</v>
@@ -4771,7 +4771,7 @@
         <v>272</v>
       </c>
       <c r="E112" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>273</v>
@@ -4794,7 +4794,7 @@
         <v>275</v>
       </c>
       <c r="E113" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>276</v>
@@ -4820,7 +4820,7 @@
         <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>279</v>
@@ -4843,7 +4843,7 @@
         <v>281</v>
       </c>
       <c r="E115" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>282</v>
@@ -4866,7 +4866,7 @@
         <v>284</v>
       </c>
       <c r="E116" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>285</v>
@@ -4889,7 +4889,7 @@
         <v>287</v>
       </c>
       <c r="E117" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>288</v>
@@ -4906,7 +4906,7 @@
         <v>289</v>
       </c>
       <c r="E118" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4923,7 +4923,7 @@
         <v>291</v>
       </c>
       <c r="E119" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>292</v>
@@ -4940,7 +4940,7 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
@@ -4951,7 +4951,7 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4968,7 +4968,7 @@
         <v>296</v>
       </c>
       <c r="E122" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>297</v>
@@ -4985,7 +4985,7 @@
         <v>298</v>
       </c>
       <c r="E123" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5002,7 +5002,7 @@
         <v>300</v>
       </c>
       <c r="E124" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>301</v>
@@ -5019,7 +5019,7 @@
         <v>302</v>
       </c>
       <c r="E125" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5036,7 +5036,7 @@
         <v>304</v>
       </c>
       <c r="E126" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>305</v>
@@ -5059,7 +5059,7 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>308</v>
@@ -5076,7 +5076,7 @@
         <v>309</v>
       </c>
       <c r="E128" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
@@ -5087,7 +5087,7 @@
         <v>310</v>
       </c>
       <c r="E129" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5104,7 +5104,7 @@
         <v>312</v>
       </c>
       <c r="E130" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>313</v>
@@ -5121,7 +5121,7 @@
         <v>314</v>
       </c>
       <c r="E131" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
@@ -5138,7 +5138,7 @@
         <v>316</v>
       </c>
       <c r="E132" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>317</v>
@@ -5161,7 +5161,7 @@
         <v>319</v>
       </c>
       <c r="E133" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>320</v>
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="E134" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5195,7 +5195,7 @@
         <v>323</v>
       </c>
       <c r="E135" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>324</v>
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="E136" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>327</v>
@@ -5235,7 +5235,7 @@
         <v>328</v>
       </c>
       <c r="E137" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5252,7 +5252,7 @@
         <v>330</v>
       </c>
       <c r="E138" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>331</v>
@@ -5269,7 +5269,7 @@
         <v>332</v>
       </c>
       <c r="E139" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5286,7 +5286,7 @@
         <v>334</v>
       </c>
       <c r="E140" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>335</v>
@@ -5309,7 +5309,7 @@
         <v>337</v>
       </c>
       <c r="E141" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>338</v>
@@ -5332,7 +5332,7 @@
         <v>340</v>
       </c>
       <c r="E142" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>341</v>
@@ -5349,7 +5349,7 @@
         <v>342</v>
       </c>
       <c r="E143" t="s">
-        <v>626</v>
+        <v>695</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5366,7 +5366,7 @@
         <v>344</v>
       </c>
       <c r="E144" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>345</v>
@@ -5383,7 +5383,7 @@
         <v>346</v>
       </c>
       <c r="E145" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -5400,7 +5400,7 @@
         <v>348</v>
       </c>
       <c r="E146" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>349</v>
@@ -5417,7 +5417,7 @@
         <v>350</v>
       </c>
       <c r="E147" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
@@ -5428,7 +5428,7 @@
         <v>351</v>
       </c>
       <c r="E148" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5445,7 +5445,7 @@
         <v>353</v>
       </c>
       <c r="E149" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>354</v>
@@ -5462,7 +5462,7 @@
         <v>355</v>
       </c>
       <c r="E150" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5479,7 +5479,7 @@
         <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>358</v>
@@ -5496,7 +5496,7 @@
         <v>359</v>
       </c>
       <c r="E152" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5513,7 +5513,7 @@
         <v>361</v>
       </c>
       <c r="E153" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>362</v>
@@ -5536,7 +5536,7 @@
         <v>364</v>
       </c>
       <c r="E154" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>365</v>
@@ -5553,7 +5553,7 @@
         <v>366</v>
       </c>
       <c r="E155" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
@@ -5564,7 +5564,7 @@
         <v>367</v>
       </c>
       <c r="E156" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
@@ -5575,7 +5575,7 @@
         <v>368</v>
       </c>
       <c r="E157" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5592,7 +5592,7 @@
         <v>370</v>
       </c>
       <c r="E158" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>371</v>
@@ -5615,7 +5615,7 @@
         <v>373</v>
       </c>
       <c r="E159" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>374</v>
@@ -5632,7 +5632,7 @@
         <v>375</v>
       </c>
       <c r="E160" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5649,7 +5649,7 @@
         <v>377</v>
       </c>
       <c r="E161" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>378</v>
@@ -5666,7 +5666,7 @@
         <v>379</v>
       </c>
       <c r="E162" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
@@ -5677,7 +5677,7 @@
         <v>380</v>
       </c>
       <c r="E163" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5694,7 +5694,7 @@
         <v>382</v>
       </c>
       <c r="E164" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>483</v>
@@ -5711,7 +5711,7 @@
         <v>383</v>
       </c>
       <c r="E165" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5728,7 +5728,7 @@
         <v>385</v>
       </c>
       <c r="E166" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>386</v>
@@ -5745,7 +5745,7 @@
         <v>387</v>
       </c>
       <c r="E167" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5762,7 +5762,7 @@
         <v>389</v>
       </c>
       <c r="E168" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>390</v>
@@ -5779,7 +5779,7 @@
         <v>391</v>
       </c>
       <c r="E169" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5796,7 +5796,7 @@
         <v>393</v>
       </c>
       <c r="E170" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>394</v>
@@ -5813,7 +5813,7 @@
         <v>395</v>
       </c>
       <c r="E171" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
@@ -5824,7 +5824,7 @@
         <v>396</v>
       </c>
       <c r="E172" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5841,7 +5841,7 @@
         <v>398</v>
       </c>
       <c r="E173" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>399</v>
@@ -5858,7 +5858,7 @@
         <v>400</v>
       </c>
       <c r="E174" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -5875,7 +5875,7 @@
         <v>402</v>
       </c>
       <c r="E175" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>484</v>
@@ -5892,7 +5892,7 @@
         <v>403</v>
       </c>
       <c r="E176" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5909,7 +5909,7 @@
         <v>405</v>
       </c>
       <c r="E177" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>406</v>
@@ -5932,7 +5932,7 @@
         <v>408</v>
       </c>
       <c r="E178" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>409</v>
@@ -5955,7 +5955,7 @@
         <v>411</v>
       </c>
       <c r="E179" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>412</v>
@@ -5972,7 +5972,7 @@
         <v>413</v>
       </c>
       <c r="E180" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5989,7 +5989,7 @@
         <v>415</v>
       </c>
       <c r="E181" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>416</v>
@@ -6006,7 +6006,7 @@
         <v>417</v>
       </c>
       <c r="E182" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
@@ -6017,7 +6017,7 @@
         <v>418</v>
       </c>
       <c r="E183" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6034,7 +6034,7 @@
         <v>420</v>
       </c>
       <c r="E184" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>421</v>
@@ -6057,7 +6057,7 @@
         <v>423</v>
       </c>
       <c r="E185" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>424</v>
@@ -6080,7 +6080,7 @@
         <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>427</v>
@@ -6097,7 +6097,7 @@
         <v>428</v>
       </c>
       <c r="E187" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6114,7 +6114,7 @@
         <v>430</v>
       </c>
       <c r="E188" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>431</v>
@@ -6131,7 +6131,7 @@
         <v>432</v>
       </c>
       <c r="E189" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -6142,7 +6142,7 @@
         <v>433</v>
       </c>
       <c r="E190" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6159,7 +6159,7 @@
         <v>435</v>
       </c>
       <c r="E191" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>436</v>
@@ -6176,7 +6176,7 @@
         <v>437</v>
       </c>
       <c r="E192" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6193,7 +6193,7 @@
         <v>439</v>
       </c>
       <c r="E193" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>485</v>
@@ -6210,7 +6210,7 @@
         <v>440</v>
       </c>
       <c r="E194" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6227,7 +6227,7 @@
         <v>442</v>
       </c>
       <c r="E195" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>443</v>
@@ -6244,7 +6244,7 @@
         <v>444</v>
       </c>
       <c r="E196" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -6261,7 +6261,7 @@
         <v>446</v>
       </c>
       <c r="E197" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>447</v>
@@ -6278,7 +6278,7 @@
         <v>448</v>
       </c>
       <c r="E198" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6295,7 +6295,7 @@
         <v>450</v>
       </c>
       <c r="E199" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>451</v>
@@ -6312,7 +6312,7 @@
         <v>452</v>
       </c>
       <c r="E200" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6329,7 +6329,7 @@
         <v>454</v>
       </c>
       <c r="E201" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>455</v>
@@ -6346,7 +6346,7 @@
         <v>456</v>
       </c>
       <c r="E202" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
@@ -6357,7 +6357,7 @@
         <v>457</v>
       </c>
       <c r="E203" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6374,7 +6374,7 @@
         <v>459</v>
       </c>
       <c r="E204" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>460</v>
@@ -6391,7 +6391,7 @@
         <v>461</v>
       </c>
       <c r="E205" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6408,7 +6408,7 @@
         <v>463</v>
       </c>
       <c r="E206" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>464</v>
@@ -6425,7 +6425,7 @@
         <v>465</v>
       </c>
       <c r="E207" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
@@ -6442,7 +6442,7 @@
         <v>467</v>
       </c>
       <c r="E208" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>468</v>
@@ -6513,7 +6513,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="C2" t="s">
         <v>469</v>
@@ -6524,7 +6524,7 @@
         <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="C3" t="s">
         <v>470</v>
@@ -6535,7 +6535,7 @@
         <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>471</v>

--- a/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
+++ b/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\anssi\rec-secu-sys-ctrl-acces-phys-videoprot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0AF98F-EBAB-4246-A1FA-3AF806A060D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9317182-A9DF-4153-9DC2-843CE2184AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1845" yWindow="-14055" windowWidth="19710" windowHeight="12330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -1496,12 +1496,6 @@
 * document répertoriant les périmètres et niveaux de privilèges des utilisateurs et des administrateurs.</t>
   </si>
   <si>
-    <t>Il est recommandé que les badges soient visuellement les plus neutres possibles. Ils ne doivent notamment pas indiquer:
-* d'informations sur l'entreprise (nom, adresse) &lt;abbr title="Si des coordonnées sont indiquées sur le dos du badge pour faciliter sa restitution en cas de perte, elles ne doivent pas mentionner explicitement le nom de l&amp;#x27;entité. Mieux vaut privilégier dans ce cas l&amp;#x27;utilisation d&amp;#x27;une boîte postale."&gt;&lt;sup&gt;24&lt;/sup&gt;&lt;/abbr&gt;;
-* d'informations sur le porteur (nom, prénom, poste), en dehors de sa photo;
-* les accès autorisés. Un numéro de traçabilité peut être indiqué sur le badge à des fins administratives, mais ce numéro doit être différent du numéro d'identification. La photographie est tolérée car elle permet de vérifier rapidement que le badge appartient bien au porteur. XXXX La puce contient l'UID et le numéro d'identification YYYY Concernant les types de badges, les supports de type puce RFID &lt;abbr title="Radio Frequency Identification."&gt;&lt;sup&gt;25&lt;/sup&gt;&lt;/abbr&gt;, comparables aux antivols dans les magasins, ne permettent que l'identification, tandis que les supports de type carte à puce, comparables aux cartes de paiement bancaire, disposent de fonctions cryptographiques qui permettent une authentification. Certaines technologies de carte d'accès, qui font appel à des mécanismes cryptographiques faibles, ont des vulnérabilités connues qui permettent leur clonage et des attaques par rejeu &lt;abbr title="Attaque dans laquelle une transmission est frauduleusement répétée par une tierce partie interceptant les paquets sur la ligne."&gt;&lt;sup&gt;26&lt;/sup&gt;&lt;/abbr&gt;. Il convient donc de s'orienter vers des produits récents, dont le niveau de sécurité est satisfaisant à date et dont le protocole de communication et la fonction anti-clone sont résistants à des attaques de niveau AV A_V AN.327.</t>
-  </si>
-  <si>
     <t>Il est recommandé d'adopter une approche prudente et sélective concernant l'installation d'applications sur les caméras de surveillance. Pour cela:
 * désactiver systématiquement les fonctionnalités non essentielles au déploiement spécifique;
 * limiter les installations aux seules applications répondant aux besoins opérationnels de l'entreprise.</t>
@@ -2155,6 +2149,12 @@
   </si>
   <si>
     <t>Procéder immédiatement à l'interruption de l'alimentation électrique &amp; déconnexion du réseau support en cas de détection d'une tentative d'intrusion physique sur platine d'interphone ou visiophone IP.</t>
+  </si>
+  <si>
+    <t>Il est recommandé que les badges soient visuellement les plus neutres possibles. Ils ne doivent notamment pas indiquer:
+* d'informations sur l'entreprise (nom, adresse) &lt;abbr title="Si des coordonnées sont indiquées sur le dos du badge pour faciliter sa restitution en cas de perte, elles ne doivent pas mentionner explicitement le nom de l&amp;#x27;entité. Mieux vaut privilégier dans ce cas l&amp;#x27;utilisation d&amp;#x27;une boîte postale."&gt;&lt;sup&gt;24&lt;/sup&gt;&lt;/abbr&gt;;
+* d'informations sur le porteur (nom, prénom, poste), en dehors de sa photo;
+* les accès autorisés. Un numéro de traçabilité peut être indiqué sur le badge à des fins administratives, mais ce numéro doit être différent du numéro d'identification. La photographie est tolérée car elle permet de vérifier rapidement que le badge appartient bien au porteur.</t>
   </si>
 </sst>
 </file>
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
@@ -2674,7 +2674,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -2745,7 +2745,7 @@
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -2756,7 +2756,7 @@
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -2773,7 +2773,7 @@
         <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>477</v>
@@ -2793,7 +2793,7 @@
         <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -2804,7 +2804,7 @@
         <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -2821,7 +2821,7 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>40</v>
@@ -2838,7 +2838,7 @@
         <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2855,7 +2855,7 @@
         <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>44</v>
@@ -2872,7 +2872,7 @@
         <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2889,7 +2889,7 @@
         <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>48</v>
@@ -2912,7 +2912,7 @@
         <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>51</v>
@@ -2929,7 +2929,7 @@
         <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2946,7 +2946,7 @@
         <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>55</v>
@@ -2963,7 +2963,7 @@
         <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -2980,7 +2980,7 @@
         <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>59</v>
@@ -2997,7 +2997,7 @@
         <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3014,7 +3014,7 @@
         <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>63</v>
@@ -3031,7 +3031,7 @@
         <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3048,7 +3048,7 @@
         <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>67</v>
@@ -3065,7 +3065,7 @@
         <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -3076,7 +3076,7 @@
         <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3093,7 +3093,7 @@
         <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>72</v>
@@ -3116,7 +3116,7 @@
         <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>75</v>
@@ -3139,7 +3139,7 @@
         <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>79</v>
@@ -3156,7 +3156,7 @@
         <v>80</v>
       </c>
       <c r="E26" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -3167,7 +3167,7 @@
         <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3184,7 +3184,7 @@
         <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>84</v>
@@ -3201,7 +3201,7 @@
         <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3218,7 +3218,7 @@
         <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>88</v>
@@ -3241,7 +3241,7 @@
         <v>90</v>
       </c>
       <c r="E31" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>91</v>
@@ -3258,7 +3258,7 @@
         <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3275,7 +3275,7 @@
         <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>95</v>
@@ -3298,7 +3298,7 @@
         <v>97</v>
       </c>
       <c r="E34" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>98</v>
@@ -3315,7 +3315,7 @@
         <v>99</v>
       </c>
       <c r="E35" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -3326,7 +3326,7 @@
         <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3343,7 +3343,7 @@
         <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>103</v>
@@ -3360,7 +3360,7 @@
         <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3377,7 +3377,7 @@
         <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>107</v>
@@ -3400,7 +3400,7 @@
         <v>109</v>
       </c>
       <c r="E40" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>110</v>
@@ -3423,7 +3423,7 @@
         <v>112</v>
       </c>
       <c r="E41" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>113</v>
@@ -3446,7 +3446,7 @@
         <v>115</v>
       </c>
       <c r="E42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>116</v>
@@ -3463,7 +3463,7 @@
         <v>117</v>
       </c>
       <c r="E43" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3480,7 +3480,7 @@
         <v>119</v>
       </c>
       <c r="E44" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>120</v>
@@ -3497,7 +3497,7 @@
         <v>121</v>
       </c>
       <c r="E45" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -3514,7 +3514,7 @@
         <v>123</v>
       </c>
       <c r="E46" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>124</v>
@@ -3537,7 +3537,7 @@
         <v>126</v>
       </c>
       <c r="E47" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>127</v>
@@ -3557,7 +3557,7 @@
         <v>128</v>
       </c>
       <c r="E48" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3574,7 +3574,7 @@
         <v>130</v>
       </c>
       <c r="E49" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>131</v>
@@ -3597,7 +3597,7 @@
         <v>133</v>
       </c>
       <c r="E50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>134</v>
@@ -3614,7 +3614,7 @@
         <v>135</v>
       </c>
       <c r="E51" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -3625,7 +3625,7 @@
         <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3642,7 +3642,7 @@
         <v>138</v>
       </c>
       <c r="E53" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>139</v>
@@ -3659,7 +3659,7 @@
         <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -3676,7 +3676,7 @@
         <v>142</v>
       </c>
       <c r="E55" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>479</v>
@@ -3693,7 +3693,7 @@
         <v>143</v>
       </c>
       <c r="E56" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3710,7 +3710,7 @@
         <v>145</v>
       </c>
       <c r="E57" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>146</v>
@@ -3727,7 +3727,7 @@
         <v>147</v>
       </c>
       <c r="E58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -3744,7 +3744,7 @@
         <v>149</v>
       </c>
       <c r="E59" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>150</v>
@@ -3767,7 +3767,7 @@
         <v>152</v>
       </c>
       <c r="E60" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>153</v>
@@ -3787,7 +3787,7 @@
         <v>154</v>
       </c>
       <c r="E61" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -3798,7 +3798,7 @@
         <v>155</v>
       </c>
       <c r="E62" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -3815,7 +3815,7 @@
         <v>157</v>
       </c>
       <c r="E63" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>158</v>
@@ -3838,7 +3838,7 @@
         <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>161</v>
@@ -3861,7 +3861,7 @@
         <v>163</v>
       </c>
       <c r="E65" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>164</v>
@@ -3881,7 +3881,7 @@
         <v>165</v>
       </c>
       <c r="E66" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3898,7 +3898,7 @@
         <v>167</v>
       </c>
       <c r="E67" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>168</v>
@@ -3921,7 +3921,7 @@
         <v>170</v>
       </c>
       <c r="E68" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>171</v>
@@ -3938,7 +3938,7 @@
         <v>172</v>
       </c>
       <c r="E69" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3949,7 +3949,7 @@
         <v>173</v>
       </c>
       <c r="E70" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -3966,7 +3966,7 @@
         <v>175</v>
       </c>
       <c r="E71" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>480</v>
@@ -3983,7 +3983,7 @@
         <v>176</v>
       </c>
       <c r="E72" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -3994,7 +3994,7 @@
         <v>177</v>
       </c>
       <c r="E73" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -4011,7 +4011,7 @@
         <v>179</v>
       </c>
       <c r="E74" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>180</v>
@@ -4037,7 +4037,7 @@
         <v>182</v>
       </c>
       <c r="E75" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>183</v>
@@ -4046,7 +4046,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>32</v>
       </c>
@@ -4060,10 +4060,10 @@
         <v>185</v>
       </c>
       <c r="E76" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>481</v>
+        <v>696</v>
       </c>
       <c r="H76" t="s">
         <v>36</v>
@@ -4083,7 +4083,7 @@
         <v>187</v>
       </c>
       <c r="E77" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>188</v>
@@ -4106,7 +4106,7 @@
         <v>190</v>
       </c>
       <c r="E78" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>191</v>
@@ -4123,7 +4123,7 @@
         <v>192</v>
       </c>
       <c r="E79" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4140,7 +4140,7 @@
         <v>194</v>
       </c>
       <c r="E80" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>195</v>
@@ -4157,7 +4157,7 @@
         <v>196</v>
       </c>
       <c r="E81" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4174,7 +4174,7 @@
         <v>198</v>
       </c>
       <c r="E82" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>199</v>
@@ -4197,7 +4197,7 @@
         <v>201</v>
       </c>
       <c r="E83" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>202</v>
@@ -4214,7 +4214,7 @@
         <v>203</v>
       </c>
       <c r="E84" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4231,7 +4231,7 @@
         <v>205</v>
       </c>
       <c r="E85" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>206</v>
@@ -4254,7 +4254,7 @@
         <v>208</v>
       </c>
       <c r="E86" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>209</v>
@@ -4277,7 +4277,7 @@
         <v>211</v>
       </c>
       <c r="E87" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>212</v>
@@ -4294,7 +4294,7 @@
         <v>213</v>
       </c>
       <c r="E88" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -4311,7 +4311,7 @@
         <v>215</v>
       </c>
       <c r="E89" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>216</v>
@@ -4328,7 +4328,7 @@
         <v>217</v>
       </c>
       <c r="E90" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4345,7 +4345,7 @@
         <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>220</v>
@@ -4362,7 +4362,7 @@
         <v>221</v>
       </c>
       <c r="E92" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4379,7 +4379,7 @@
         <v>223</v>
       </c>
       <c r="E93" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>224</v>
@@ -4402,7 +4402,7 @@
         <v>226</v>
       </c>
       <c r="E94" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>227</v>
@@ -4419,7 +4419,7 @@
         <v>228</v>
       </c>
       <c r="E95" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4436,7 +4436,7 @@
         <v>230</v>
       </c>
       <c r="E96" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>231</v>
@@ -4459,7 +4459,7 @@
         <v>233</v>
       </c>
       <c r="E97" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>234</v>
@@ -4482,7 +4482,7 @@
         <v>237</v>
       </c>
       <c r="E98" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>238</v>
@@ -4508,7 +4508,7 @@
         <v>240</v>
       </c>
       <c r="E99" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>241</v>
@@ -4531,7 +4531,7 @@
         <v>243</v>
       </c>
       <c r="E100" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>244</v>
@@ -4554,7 +4554,7 @@
         <v>246</v>
       </c>
       <c r="E101" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>247</v>
@@ -4571,7 +4571,7 @@
         <v>248</v>
       </c>
       <c r="E102" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -4582,7 +4582,7 @@
         <v>249</v>
       </c>
       <c r="E103" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4599,7 +4599,7 @@
         <v>251</v>
       </c>
       <c r="E104" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>252</v>
@@ -4622,7 +4622,7 @@
         <v>254</v>
       </c>
       <c r="E105" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>255</v>
@@ -4645,7 +4645,7 @@
         <v>257</v>
       </c>
       <c r="E106" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>258</v>
@@ -4668,7 +4668,7 @@
         <v>260</v>
       </c>
       <c r="E107" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>261</v>
@@ -4691,7 +4691,7 @@
         <v>263</v>
       </c>
       <c r="E108" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>264</v>
@@ -4714,10 +4714,10 @@
         <v>266</v>
       </c>
       <c r="E109" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H109" t="s">
         <v>36</v>
@@ -4731,7 +4731,7 @@
         <v>267</v>
       </c>
       <c r="E110" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4748,7 +4748,7 @@
         <v>269</v>
       </c>
       <c r="E111" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>270</v>
@@ -4771,7 +4771,7 @@
         <v>272</v>
       </c>
       <c r="E112" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>273</v>
@@ -4794,7 +4794,7 @@
         <v>275</v>
       </c>
       <c r="E113" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>276</v>
@@ -4820,7 +4820,7 @@
         <v>278</v>
       </c>
       <c r="E114" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>279</v>
@@ -4843,7 +4843,7 @@
         <v>281</v>
       </c>
       <c r="E115" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>282</v>
@@ -4866,7 +4866,7 @@
         <v>284</v>
       </c>
       <c r="E116" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>285</v>
@@ -4889,7 +4889,7 @@
         <v>287</v>
       </c>
       <c r="E117" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>288</v>
@@ -4906,7 +4906,7 @@
         <v>289</v>
       </c>
       <c r="E118" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4923,7 +4923,7 @@
         <v>291</v>
       </c>
       <c r="E119" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>292</v>
@@ -4940,7 +4940,7 @@
         <v>293</v>
       </c>
       <c r="E120" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
@@ -4951,7 +4951,7 @@
         <v>294</v>
       </c>
       <c r="E121" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4968,7 +4968,7 @@
         <v>296</v>
       </c>
       <c r="E122" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>297</v>
@@ -4985,7 +4985,7 @@
         <v>298</v>
       </c>
       <c r="E123" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5002,7 +5002,7 @@
         <v>300</v>
       </c>
       <c r="E124" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>301</v>
@@ -5019,7 +5019,7 @@
         <v>302</v>
       </c>
       <c r="E125" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5036,7 +5036,7 @@
         <v>304</v>
       </c>
       <c r="E126" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>305</v>
@@ -5059,7 +5059,7 @@
         <v>307</v>
       </c>
       <c r="E127" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>308</v>
@@ -5076,7 +5076,7 @@
         <v>309</v>
       </c>
       <c r="E128" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
@@ -5087,7 +5087,7 @@
         <v>310</v>
       </c>
       <c r="E129" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5104,7 +5104,7 @@
         <v>312</v>
       </c>
       <c r="E130" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>313</v>
@@ -5121,7 +5121,7 @@
         <v>314</v>
       </c>
       <c r="E131" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
@@ -5138,7 +5138,7 @@
         <v>316</v>
       </c>
       <c r="E132" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>317</v>
@@ -5161,7 +5161,7 @@
         <v>319</v>
       </c>
       <c r="E133" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>320</v>
@@ -5178,7 +5178,7 @@
         <v>321</v>
       </c>
       <c r="E134" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5195,7 +5195,7 @@
         <v>323</v>
       </c>
       <c r="E135" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>324</v>
@@ -5218,7 +5218,7 @@
         <v>326</v>
       </c>
       <c r="E136" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>327</v>
@@ -5235,7 +5235,7 @@
         <v>328</v>
       </c>
       <c r="E137" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5252,7 +5252,7 @@
         <v>330</v>
       </c>
       <c r="E138" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>331</v>
@@ -5269,7 +5269,7 @@
         <v>332</v>
       </c>
       <c r="E139" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5286,7 +5286,7 @@
         <v>334</v>
       </c>
       <c r="E140" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>335</v>
@@ -5309,7 +5309,7 @@
         <v>337</v>
       </c>
       <c r="E141" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>338</v>
@@ -5332,7 +5332,7 @@
         <v>340</v>
       </c>
       <c r="E142" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>341</v>
@@ -5349,7 +5349,7 @@
         <v>342</v>
       </c>
       <c r="E143" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5366,7 +5366,7 @@
         <v>344</v>
       </c>
       <c r="E144" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>345</v>
@@ -5383,7 +5383,7 @@
         <v>346</v>
       </c>
       <c r="E145" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -5400,7 +5400,7 @@
         <v>348</v>
       </c>
       <c r="E146" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>349</v>
@@ -5417,7 +5417,7 @@
         <v>350</v>
       </c>
       <c r="E147" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
@@ -5428,7 +5428,7 @@
         <v>351</v>
       </c>
       <c r="E148" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5445,7 +5445,7 @@
         <v>353</v>
       </c>
       <c r="E149" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>354</v>
@@ -5462,7 +5462,7 @@
         <v>355</v>
       </c>
       <c r="E150" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5479,7 +5479,7 @@
         <v>357</v>
       </c>
       <c r="E151" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>358</v>
@@ -5496,7 +5496,7 @@
         <v>359</v>
       </c>
       <c r="E152" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5513,7 +5513,7 @@
         <v>361</v>
       </c>
       <c r="E153" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>362</v>
@@ -5536,7 +5536,7 @@
         <v>364</v>
       </c>
       <c r="E154" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>365</v>
@@ -5553,7 +5553,7 @@
         <v>366</v>
       </c>
       <c r="E155" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
@@ -5564,7 +5564,7 @@
         <v>367</v>
       </c>
       <c r="E156" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
@@ -5575,7 +5575,7 @@
         <v>368</v>
       </c>
       <c r="E157" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5592,7 +5592,7 @@
         <v>370</v>
       </c>
       <c r="E158" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>371</v>
@@ -5615,7 +5615,7 @@
         <v>373</v>
       </c>
       <c r="E159" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>374</v>
@@ -5632,7 +5632,7 @@
         <v>375</v>
       </c>
       <c r="E160" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5649,7 +5649,7 @@
         <v>377</v>
       </c>
       <c r="E161" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>378</v>
@@ -5666,7 +5666,7 @@
         <v>379</v>
       </c>
       <c r="E162" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
@@ -5677,7 +5677,7 @@
         <v>380</v>
       </c>
       <c r="E163" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5694,10 +5694,10 @@
         <v>382</v>
       </c>
       <c r="E164" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H164" t="s">
         <v>36</v>
@@ -5711,7 +5711,7 @@
         <v>383</v>
       </c>
       <c r="E165" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5728,7 +5728,7 @@
         <v>385</v>
       </c>
       <c r="E166" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>386</v>
@@ -5745,7 +5745,7 @@
         <v>387</v>
       </c>
       <c r="E167" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5762,7 +5762,7 @@
         <v>389</v>
       </c>
       <c r="E168" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>390</v>
@@ -5779,7 +5779,7 @@
         <v>391</v>
       </c>
       <c r="E169" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5796,7 +5796,7 @@
         <v>393</v>
       </c>
       <c r="E170" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>394</v>
@@ -5813,7 +5813,7 @@
         <v>395</v>
       </c>
       <c r="E171" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
@@ -5824,7 +5824,7 @@
         <v>396</v>
       </c>
       <c r="E172" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5841,7 +5841,7 @@
         <v>398</v>
       </c>
       <c r="E173" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>399</v>
@@ -5858,7 +5858,7 @@
         <v>400</v>
       </c>
       <c r="E174" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -5875,10 +5875,10 @@
         <v>402</v>
       </c>
       <c r="E175" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H175" t="s">
         <v>36</v>
@@ -5892,7 +5892,7 @@
         <v>403</v>
       </c>
       <c r="E176" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5909,7 +5909,7 @@
         <v>405</v>
       </c>
       <c r="E177" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>406</v>
@@ -5932,7 +5932,7 @@
         <v>408</v>
       </c>
       <c r="E178" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>409</v>
@@ -5955,7 +5955,7 @@
         <v>411</v>
       </c>
       <c r="E179" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>412</v>
@@ -5972,7 +5972,7 @@
         <v>413</v>
       </c>
       <c r="E180" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5989,7 +5989,7 @@
         <v>415</v>
       </c>
       <c r="E181" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>416</v>
@@ -6006,7 +6006,7 @@
         <v>417</v>
       </c>
       <c r="E182" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
@@ -6017,7 +6017,7 @@
         <v>418</v>
       </c>
       <c r="E183" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6034,7 +6034,7 @@
         <v>420</v>
       </c>
       <c r="E184" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>421</v>
@@ -6057,7 +6057,7 @@
         <v>423</v>
       </c>
       <c r="E185" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>424</v>
@@ -6080,7 +6080,7 @@
         <v>426</v>
       </c>
       <c r="E186" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>427</v>
@@ -6097,7 +6097,7 @@
         <v>428</v>
       </c>
       <c r="E187" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6114,7 +6114,7 @@
         <v>430</v>
       </c>
       <c r="E188" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>431</v>
@@ -6131,7 +6131,7 @@
         <v>432</v>
       </c>
       <c r="E189" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -6142,7 +6142,7 @@
         <v>433</v>
       </c>
       <c r="E190" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6159,7 +6159,7 @@
         <v>435</v>
       </c>
       <c r="E191" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>436</v>
@@ -6176,7 +6176,7 @@
         <v>437</v>
       </c>
       <c r="E192" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6193,10 +6193,10 @@
         <v>439</v>
       </c>
       <c r="E193" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H193" t="s">
         <v>36</v>
@@ -6210,7 +6210,7 @@
         <v>440</v>
       </c>
       <c r="E194" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6227,7 +6227,7 @@
         <v>442</v>
       </c>
       <c r="E195" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>443</v>
@@ -6244,7 +6244,7 @@
         <v>444</v>
       </c>
       <c r="E196" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -6261,7 +6261,7 @@
         <v>446</v>
       </c>
       <c r="E197" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>447</v>
@@ -6278,7 +6278,7 @@
         <v>448</v>
       </c>
       <c r="E198" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6295,7 +6295,7 @@
         <v>450</v>
       </c>
       <c r="E199" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>451</v>
@@ -6312,7 +6312,7 @@
         <v>452</v>
       </c>
       <c r="E200" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6329,7 +6329,7 @@
         <v>454</v>
       </c>
       <c r="E201" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>455</v>
@@ -6346,7 +6346,7 @@
         <v>456</v>
       </c>
       <c r="E202" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
@@ -6357,7 +6357,7 @@
         <v>457</v>
       </c>
       <c r="E203" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6374,7 +6374,7 @@
         <v>459</v>
       </c>
       <c r="E204" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>460</v>
@@ -6391,7 +6391,7 @@
         <v>461</v>
       </c>
       <c r="E205" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6408,7 +6408,7 @@
         <v>463</v>
       </c>
       <c r="E206" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>464</v>
@@ -6425,7 +6425,7 @@
         <v>465</v>
       </c>
       <c r="E207" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
@@ -6442,7 +6442,7 @@
         <v>467</v>
       </c>
       <c r="E208" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>468</v>
@@ -6513,7 +6513,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C2" t="s">
         <v>469</v>
@@ -6524,7 +6524,7 @@
         <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C3" t="s">
         <v>470</v>
@@ -6535,7 +6535,7 @@
         <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>471</v>

--- a/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
+++ b/tools/excel/anssi/rec-secu-sys-ctrl-acces-phys-videoprot/anssi_rec-secu-sys-ctrl-acces-phys-videoprot_v2.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\anssi\rec-secu-sys-ctrl-acces-phys-videoprot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9317182-A9DF-4153-9DC2-843CE2184AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46E83BD-907C-4691-8CD9-DE393F6F6593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="-14055" windowWidth="19710" windowHeight="12330" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="593">
   <si>
     <t>type</t>
   </si>
@@ -138,105 +138,51 @@
     <t>3</t>
   </si>
   <si>
-    <t>r1</t>
-  </si>
-  <si>
-    <t>[R1]</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
     <t>3.1</t>
   </si>
   <si>
-    <t>r2</t>
-  </si>
-  <si>
-    <t>[R2]</t>
-  </si>
-  <si>
     <t>Il est nécessaire de référencer de manière exhaustive les sites à contrôler en prenant en compte leurs particularités.</t>
   </si>
   <si>
     <t>3.2</t>
   </si>
   <si>
-    <t>r3</t>
-  </si>
-  <si>
-    <t>[R3]</t>
-  </si>
-  <si>
     <t>Il est recommandé d'identifier, au travers d'une analyse de risque, les valeurs métier et les biens supports sur lesquels elles s'appuient, pour déterminer les ressources qu'il convient de protéger, et définir le niveau de protection attendu associé à chaque site référencé.</t>
   </si>
   <si>
     <t>3.3</t>
   </si>
   <si>
-    <t>r4</t>
-  </si>
-  <si>
-    <t>[R4]</t>
-  </si>
-  <si>
     <t>Les zones où sont situés les éléments du système de contrôle d'accès ou de vidéoprotection (serveurs du centre de gestion du système, et stations de travail) doivent être définies au niveau de protection attendu le plus élevé.</t>
   </si>
   <si>
-    <t>r5</t>
-  </si>
-  <si>
-    <t>[R5]</t>
-  </si>
-  <si>
     <t>Il est recommandé qu'une échelle précise et explicite des niveaux de protection attendus avec leurs définitions associées soit établie. Il est ensuite recommandé que les sites à protéger soient découpés en zones classées par niveau de protection attendu selon cette échelle.</t>
   </si>
   <si>
     <t>3.4</t>
   </si>
   <si>
-    <t>r6</t>
-  </si>
-  <si>
-    <t>[R6]</t>
-  </si>
-  <si>
     <t>Il est recommandé qu'une analyse de risque soit menée afin d'identifier, pour chaque site à contrôler, les niveaux de sûreté des équipements et installations de contrôles d'accès physique nécessaires.</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>r7</t>
-  </si>
-  <si>
-    <t>[R7]</t>
-  </si>
-  <si>
     <t>Dans le but de connaître les besoins de chaque point d'accès à contrôler, il est recommandé d'identifier les flux de circulation des individus.</t>
   </si>
   <si>
     <t>3.6</t>
   </si>
   <si>
-    <t>r8</t>
-  </si>
-  <si>
-    <t>[R8]</t>
-  </si>
-  <si>
     <t>Les différents acteurs intervenant dans les processus organisationnels de gestion des accès physiques et de vidéoprotection doivent être clairement identifiés pour que leurs droits d'accès soient calculés au plus juste. Dans les cas où plusieurs rôles sont susceptibles d'être assurés par les mêmes personnes, il faut s'assurer de la pertinence des droits résultant de ces cumuls (voir la section 10.4).</t>
   </si>
   <si>
     <t>3.7</t>
   </si>
   <si>
-    <t>r9</t>
-  </si>
-  <si>
-    <t>[R9]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé que les processus organisationnels décrivant les échanges entre les acteurs de la gestion des accès physiques et de la vidéoprotection pour la réalisation d'un objectif particulier soient clairement définis et formalisés.</t>
   </si>
   <si>
@@ -246,33 +192,18 @@
     <t>4.1</t>
   </si>
   <si>
-    <t>r10</t>
-  </si>
-  <si>
-    <t>[R10]</t>
-  </si>
-  <si>
     <t>Les SI de contrôle d'accès et de vidéoprotection doivent être cloisonnés des autres composantes du système d'information de l'entité. Il est hautement recommandé qu'un cloisonnement physique (câblage et équipements réseau dédiés) soit privilégié par rapport à un cloisonnement logique (VLAN par exemple), dont le niveau de robustesse peut être insuffisant dans ce contexte.</t>
   </si>
   <si>
     <t>r10m</t>
   </si>
   <si>
-    <t>[R10-]</t>
-  </si>
-  <si>
     <t>À défaut d'un cloisonnement physique, il est recommandé de cloisonner logiquement les SI de contrôle d'accès et de vidéoprotection par rapport aux autres composantes du SI de l'entité en mettant en oeuvre des mécanismes de filtrage, de chiffrement et d'authentification de réseau reposant sur le protocole IPsec. La mise en oeuvre du protocole IPsec doit être conforme aux recommandations du guide de l'ANSSI [[7]](https://cyber.gouv.fr/guide-ipsec).</t>
   </si>
   <si>
     <t>R-</t>
   </si>
   <si>
-    <t>r11</t>
-  </si>
-  <si>
-    <t>[R11]</t>
-  </si>
-  <si>
     <t>Lorsque l'architecture globale inclut des zones de niveau de protection attendu différentes alors les zones de même niveau de protection attendu doivent bénéficier d'un SI de contrôle d'accès ou de vidéoprotection qui leur est dédié. Il faut dans ce cas considérer chaque ensemble de même niveau de protection attendu comme un SI à part entière.</t>
   </si>
   <si>
@@ -282,54 +213,27 @@
     <t>4.2.1</t>
   </si>
   <si>
-    <t>r12</t>
-  </si>
-  <si>
-    <t>[R12]</t>
-  </si>
-  <si>
     <t>Il est recommandé que les liaisons filaires ne soient ni apparentes ni situées dans une zone non contrôlée. Dans le cas des liaisons filaires associées aux caméras extérieures, elles doivent être si possible non apparentes et protégées physiquement (encastrées, bien enterrées, etc.).</t>
   </si>
   <si>
     <t>4.2.2</t>
   </si>
   <si>
-    <t>r13</t>
-  </si>
-  <si>
-    <t>[R13]</t>
-  </si>
-  <si>
     <t>Il est recommandé de privilégier la mise en place de connexions point à point &lt;abbr title="Une connexion point à point est une connexion directe sans équipement intermédiaire de commutation ou de concentration."&gt;&lt;sup&gt;16&lt;/sup&gt;&lt;/abbr&gt; sur les liaisons entre les têtes de lecture et l'UTL. L'UTL étant le dispositif le plus proche d'une tête de lecture, il convient de s'assurer de l'homogénéité du niveau de protection des zones où se situent les têtes de lecture qui lui sont rattachées.</t>
   </si>
   <si>
-    <t>r14</t>
-  </si>
-  <si>
-    <t>[R14]</t>
-  </si>
-  <si>
     <t>Une UTL ne doit desservir que des têtes de lecture contrôlant l'accès à des zones dont le niveau de protection attendu est identique.</t>
   </si>
   <si>
     <t>4.2.3</t>
   </si>
   <si>
-    <t>r15</t>
-  </si>
-  <si>
-    <t>[R15]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de privilégier la connectivité filaire à la connectivité sans-fil pour les dispositifs de vidéoprotection comme pour les dispositifs de contrôle d'accès physique.</t>
   </si>
   <si>
     <t>r15m</t>
   </si>
   <si>
-    <t>[R15-]</t>
-  </si>
-  <si>
     <t>Dans le cas où le choix de la liaison sans-fil est obligatoire, il est recommandé de s'orienter vers des solutions proposant un deuxième chiffrement, en plus du chiffrement opéré par la liaison sans-fil. Les flux doivent être authentifiés, et protégés en confidentialité et en intégrité. Les opérations de chiffrement et de déchiffrement doivent s'effectuer en zone contrôlée. La borne d'accès sans-fil doit être placée à l'intérieur de la zone contrôlée.</t>
   </si>
   <si>
@@ -339,105 +243,54 @@
     <t>4.3.1</t>
   </si>
   <si>
-    <t>r16</t>
-  </si>
-  <si>
-    <t>[R16]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de mettre en oeuvre un cloisonnement logique entre les dispositifs au sein du réseau support. En particulier, dans la mesure où les différents dispositifs n'ont pas de raison légitime de communiquer entre eux directement,</t>
   </si>
   <si>
     <t>4.3.2</t>
   </si>
   <si>
-    <t>r17</t>
-  </si>
-  <si>
-    <t>[R17]</t>
-  </si>
-  <si>
     <t>Les points d'accès au réseau des dispositifs comme les UTL ou les caméras constituant une vulnérabilité, il est recommandé qu'ils ne soient ni apparents ni accessibles facilement.</t>
   </si>
   <si>
-    <t>r18</t>
-  </si>
-  <si>
-    <t>[R18]</t>
-  </si>
-  <si>
     <t>Les ports inutilisés sur les commutateurs réseau doivent être désactivés.</t>
   </si>
   <si>
-    <t>r19</t>
-  </si>
-  <si>
-    <t>[R19]</t>
-  </si>
-  <si>
     <t>Afin de limiter les possibilités d'accès illégitimes au réseau via le port d'accès d'un équipement, il est recommandé de mettre en oeuvre une authentification cryptographique des accès au réseau comme le protocole 802.1X, dans la mesure où les dispositifs connectés supportent ce protocole. Dans ce cas, il est recommandé que le déploiement du réseau 802.1X s'appuie sur les recommandations mentionnées dans le guide de l'ANSSI sur sa mise en oeuvre [[2]](https://cyber.gouv.fr/guide-802-1x).</t>
   </si>
   <si>
     <t>r19m</t>
   </si>
   <si>
-    <t>[R19-]</t>
-  </si>
-  <si>
     <t>Dans le cas où les dispositifs ne supportent pas le protocole 802.1X, il est recommandé, par défaut, que les accès aux ports réseau soient contrôlés par la vérification de la légitimité des adresses MAC des dispositifs qui se connectent.</t>
   </si>
   <si>
     <t>4.3.3</t>
   </si>
   <si>
-    <t>r20</t>
-  </si>
-  <si>
-    <t>[R20]</t>
-  </si>
-  <si>
     <t>Lorsque l'analyse de risque prévoit la mutualisation au sein d'un même réseau support de dispositifs de contrôle d'accès physique associés à des zones de niveaux de protection attendus distincts, il est recommandé de mettre en place un cloisonnement logique (ex.: VLAN) entre ces dispositifs.</t>
   </si>
   <si>
     <t>4.3.4</t>
   </si>
   <si>
-    <t>r21</t>
-  </si>
-  <si>
-    <t>[R21]</t>
-  </si>
-  <si>
     <t>Il est recommandé de ne pas mutualiser sur un même réseau support les dispositifs de contrôle d'accès physique et ceux associés à la vidéoprotection.</t>
   </si>
   <si>
     <t>r21m</t>
   </si>
   <si>
-    <t>[R21-]</t>
-  </si>
-  <si>
     <t>Lorsque la mutualisation de dispositifs de vidéoprotection et de contrôle d'accès physique sur des réseaux support communs s'avère incontournable et que les zones contrôlées par ces dispositifs nécessitent un même niveau de protection, il est recommandé de mettre en place un cloisonnement logique (ex.: VLAN) entre ces dispositifs.</t>
   </si>
   <si>
     <t>4.3.5</t>
   </si>
   <si>
-    <t>r22</t>
-  </si>
-  <si>
-    <t>[R22]</t>
-  </si>
-  <si>
     <t>Il est recommandé de déployer les caméras situées en dehors de la zone contrôlée sur un réseau support physiquement dédié et distinct des autres réseaux support incluant les caméras situées dans la zone contrôlée.</t>
   </si>
   <si>
     <t>r22m</t>
   </si>
   <si>
-    <t>[R22-]</t>
-  </si>
-  <si>
     <t>À défaut d'un cloisonnement physique, les caméras situées en dehors de la zone contrôlée doivent être déployées sur un réseau logique dédié à cet usage en mettant en oeuvre des mécanismes de cloisonnement logique, de filtrage, de chiffrement et d'authentification de réseau (IPsec). La mise en oeuvre du protocole IPsec doit être conforme aux recommandations du guide de l'ANSSI [[7]](https://cyber.gouv.fr/guide-ipsec).</t>
   </si>
   <si>
@@ -447,54 +300,27 @@
     <t>4.4.1</t>
   </si>
   <si>
-    <t>r23</t>
-  </si>
-  <si>
-    <t>[R23]</t>
-  </si>
-  <si>
     <t>Les flux en provenance et à destination des réseaux support doivent être filtrés par un ou plusieurs pare-feux. Il est recommandé de bloquer par défaut tous les flux entre les réseaux support et de n'autoriser que les flux strictement nécessaires au fonctionnement du système.</t>
   </si>
   <si>
     <t>4.4.2</t>
   </si>
   <si>
-    <t>r24</t>
-  </si>
-  <si>
-    <t>[R24]</t>
-  </si>
-  <si>
     <t>4.4.3</t>
   </si>
   <si>
-    <t>r25</t>
-  </si>
-  <si>
-    <t>[R25]</t>
-  </si>
-  <si>
     <t>Si les flux de contrôle d'accès ou de vidéoprotection en provenance de sites distants circulent sur un réseau de transport non maîtrisé, ces flux doivent être chiffrés et authentifiés depuis le site distant jusqu'au site où est localisé le centre de gestion correspondant. Dans ce cas, un tunnel IPsec entre les sites concernés doit être établi conformément aux recommandations du guide de l'ANSSI [[7]](https://cyber.gouv.fr/guide-ipsec).</t>
   </si>
   <si>
     <t>4.5</t>
   </si>
   <si>
-    <t>r26</t>
-  </si>
-  <si>
-    <t>[R26]</t>
-  </si>
-  <si>
     <t>Il est recommandé d'éviter de recourir à l'externalisation des services de gestion de contrôle d'accès ou de vidéoprotection chez un prestataire de services.</t>
   </si>
   <si>
     <t>r26m</t>
   </si>
   <si>
-    <t>[R26-]</t>
-  </si>
-  <si>
     <t>Si l'externalisation des services de gestion du contrôle d'accès ou de vidéoprotection sur un service d'informatique en nuage ou chez un prestataire de services s'avère incontournable, il est recommandé que le choix du prestataire de services s'oriente</t>
   </si>
   <si>
@@ -504,51 +330,27 @@
     <t>4.6.1</t>
   </si>
   <si>
-    <t>r27</t>
-  </si>
-  <si>
-    <t>[R27]</t>
-  </si>
-  <si>
     <t>Dans la mesure du possible, il est recommandé d'éviter d'interconnecter le système de contrôle d'accès physique avec le SI de l'entité.</t>
   </si>
   <si>
     <t>r27m</t>
   </si>
   <si>
-    <t>[R27-]</t>
-  </si>
-  <si>
     <t>Dans le cas où une interconnexion entre le GAC et un serveur du SI de l'entité serait incontournable, il est recommandé de filtrer tous les accès entre le GAC et le SI de l'entité. Seuls les flux concernés par le besoin d'interconnexion doivent être autorisés.</t>
   </si>
   <si>
-    <t>r28</t>
-  </si>
-  <si>
-    <t>[R28]</t>
-  </si>
-  <si>
     <t>Il est recommandé que les flux échangés entre un système de contrôle d'accès physique et le SI soient protégés en intégrité, en authenticité et en confidentialité à l'aide de protocoles cryptographiques éprouvés comme TLS ou, mieux, IPsec.</t>
   </si>
   <si>
     <t>4.6.2</t>
   </si>
   <si>
-    <t>r29</t>
-  </si>
-  <si>
-    <t>[R29]</t>
-  </si>
-  <si>
     <t>Dans le cas où des échanges entre des systèmes de contrôle d'accès et de vidéoprotection sont nécessaires, il convient de privilégier une solution s'appuyant sur deux centres de gestion et deux réseaux fédérateurs distincts avec une interconnexion entre les deux centres de gestion. Il est recommandé dans ce cas de chiffrer et d'authentifier les flux entre les deux centres de gestion et de n'autoriser que les flux métier strictement nécessaires.</t>
   </si>
   <si>
     <t>r29m</t>
   </si>
   <si>
-    <t>[R29-]</t>
-  </si>
-  <si>
     <t>Si l'utilisation d'un centre de gestion commun aux systèmes de contrôle d'accès et de vidéoprotection s'avère incontournable, il faut s'assurer que les recommandations R23 sur le filtrage des flux entre les réseaux support et R24 sur le filtrage des flux entre les réseaux support et le réseau du centre de gestion sont bien appliquées.</t>
   </si>
   <si>
@@ -558,225 +360,99 @@
     <t>5.3</t>
   </si>
   <si>
-    <t>r30</t>
-  </si>
-  <si>
-    <t>[R30]</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
     <t>6.1</t>
   </si>
   <si>
-    <t>r31</t>
-  </si>
-  <si>
-    <t>[R31]</t>
-  </si>
-  <si>
     <t>Les données relatives aux droits d'accès, aux périodes de validité et aux informations d'authentification autres que le numéro d'identification ne doivent pas être stockées dans le badge. Dès lors il est recommandé que ces informations soient stockées dans la base de données du GAC.</t>
   </si>
   <si>
     <t>r31m</t>
   </si>
   <si>
-    <t>[R31-]</t>
-  </si>
-  <si>
     <t>Lorsque la biométrie est utilisée comme second facteur d'authentification, les données relatives aux gabarits biométriques peuvent être stockées sur le badge s'il résiste au minimum aux attaques de niveau AV A_V AN.5.</t>
   </si>
   <si>
-    <t>r32</t>
-  </si>
-  <si>
-    <t>[R32]</t>
-  </si>
-  <si>
-    <t>r33</t>
-  </si>
-  <si>
-    <t>[R33]</t>
-  </si>
-  <si>
     <t>Dans la mesure du possible, il faut privilégier l'emploi de cartes d'accès intégrant un composant sous-jacent qui inclut la fonctionnalité de communication et qui a été certifié Critères Communs avec une résistance aux attaques de niveau AV A_V AN.3.</t>
   </si>
   <si>
-    <t>r34</t>
-  </si>
-  <si>
-    <t>[R34]</t>
-  </si>
-  <si>
     <t>Un badge doit être garanti unique. Aucun doublon ne doit être possible sur le même système ni sur un système existant dans l'entité ou hors de l'entité. Un badge doit pouvoir être réaffecté à une autre personne sans perte de traçabilité.</t>
   </si>
   <si>
     <t>6.2</t>
   </si>
   <si>
-    <t>r35</t>
-  </si>
-  <si>
-    <t>[R35]</t>
-  </si>
-  <si>
     <t>Il est fortement déconseillé de recourir aux technologies de badges virtuels sur ordiphone qui n'offrent aucune garantie quant au stockage sécurisé des secrets liés au contrôle d'accès physique. De plus, la portée de la technologie Bluetooth n'est pas adaptée au contrôle d'accès de locaux, et les multiples usages possibles de la technologie NFC sur l'ordiphone apportent une complexité supplémentaire qui peut s'avérer délicate à gérer.</t>
   </si>
   <si>
     <t>6.3</t>
   </si>
   <si>
-    <t>r36</t>
-  </si>
-  <si>
-    <t>[R36]</t>
-  </si>
-  <si>
     <t>Les parties du système situées hors de la zone contrôlée, incluant les têtes de lecture, sont potentiellement des sources de vulnérabilités. Il est donc recommandé d'anonymiser les éléments apparents des têtes de lecture, et de contrôler minutieusement la liste des personnes habilitées à intervenir sur ces dispositifs.</t>
   </si>
   <si>
-    <t>r37</t>
-  </si>
-  <si>
-    <t>[R37]</t>
-  </si>
-  <si>
     <t>Les informations liées au second facteur d'authentification, échangées entre le dispositif rattaché à la tête de lecture et l'UTL, doivent être protégées en intégrité et en confidentialité.</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>r38</t>
-  </si>
-  <si>
-    <t>[R38]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé que les UTL soient situées à l'intérieur de la zone contrôlée dont elles commandent l'accès et ne soient pas accessibles facilement. Idéalement, elles doivent être à l'abri de tout accès frauduleux, dans un local technique fermé ou tout autre type d'emplacement sécurisé.</t>
   </si>
   <si>
-    <t>r39</t>
-  </si>
-  <si>
-    <t>[R39]</t>
-  </si>
-  <si>
     <t>Il est impératif de disposer de la liste des personnes autorisées à accéder physiquement aux UTL et d'assurer également la surveillance des opérations effectuées sur ces équipements.</t>
   </si>
   <si>
-    <t>r40</t>
-  </si>
-  <si>
-    <t>[R40]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé que les communications entre les UTL ainsi que les communications entre les UTL et le centre de gestion soient protégées en intégrité et confidentialité, et que le mécanisme de chiffrement soit choisi et implémenté dans le respect des préconisations mentionnées dans le référentiel général de sécurité (RGS) [[18]](https://cyber.gouv.fr/rgs) publié par l'ANSSI.</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>r41</t>
-  </si>
-  <si>
-    <t>[R41]</t>
-  </si>
-  <si>
     <t>La configuration type n°1 est hautement recommandée. Elle reporte néanmoins le risque de l'exploitation d'une vulnérabilité de la tête de lecture sur l'UTL. Ainsi, les mesures de protection concernant l'UTL requièrent une attention toute particulière, notamment pour la protection des clés cryptographiques (voir la recommandation R38). L'implémentation de la configuration type n°2 est déconseillée car la tête de lecture, située en zone non contrôlée, renferme des éléments secrets. Cette implémentation ne peut donc s'envisager que si la tête de lecture a fait l'objet d'une étude de sécurité approfondie. Les configurations type n°3 et n°4 sont à proscrire car dans un cas le badge peut être cloné, et dans l'autre cas la liaison filaire n'est pas protégée.</t>
   </si>
   <si>
     <t>6.6</t>
   </si>
   <si>
-    <t>r42</t>
-  </si>
-  <si>
-    <t>[R42]</t>
-  </si>
-  <si>
     <t>Le centre de gestion du contrôle d'accès physique doit être considéré comme un SI à part entière. À ce titre, il est primordial de rappeler la nécessité de sécuriser l'ensemble des éléments constituant ce SI. Il est fortement recommandé d'appliquer strictement les règles d'hygiène informatique telles que décrites dans le guide de l'ANSSI consacré à ce sujet [[4]](https://cyber.gouv.fr/hygiene-informatique).</t>
   </si>
   <si>
     <t>6.8</t>
   </si>
   <si>
-    <t>r43</t>
-  </si>
-  <si>
-    <t>[R43]</t>
-  </si>
-  <si>
     <t>La mise en oeuvre d'un système de contrôle d'accès physique avec gestion centralisée est nécessaire pour protéger un périmètre donné. En complément, et de manière optionnelle, un système de contrôle d'accès physique sans GAC peut être utilisé pour contrôler l'accès à des sous-zones au sein de ce périmètre.</t>
   </si>
   <si>
-    <t>r44</t>
-  </si>
-  <si>
-    <t>[R44]</t>
-  </si>
-  <si>
     <t>Lorsqu'un porteur de badge se présente devant une zone contrôlée par un système de contrôle d'accès physique sans GAC, le niveau de protection de la zone contrôlée est identique à celui de la zone où se situe la tête de lecture sur laquelle l'usager a badgé. Le franchissement d'un contrôle d'accès physique sans GAC ne permet pas l'élévation du niveau de protection de la zone contrôlée.</t>
   </si>
   <si>
     <t>6.9</t>
   </si>
   <si>
-    <t>r45</t>
-  </si>
-  <si>
-    <t>[R45]</t>
-  </si>
-  <si>
     <t>L'interphone ou le visiophone a la capacité fonctionnelle de déclencher l'ouverture d'une porte grâce à un relais. Cette fonctionnalité ne doit jamais être câblée. La décision de déclenchement d'une ouverture doit uniquement revenir à une UTL située en zone contrôlée.</t>
   </si>
   <si>
     <t>r46p</t>
   </si>
   <si>
-    <t>[R46+]</t>
-  </si>
-  <si>
     <t>L'emploi de technologies différentes au sein des réseaux de vidéoprotection en zones contrôlées et non contrôlées apporte une sécurité supplémentaire, en limitant les risques de voir une même vulnérabilité exploitée sur les deux réseaux. Il est recommandé de privilégier l'usage de technologies analogiques pour les interphones et visiophones situés sur le réseau externe, c'est à dire en dehors de la zone contrôlée.</t>
   </si>
   <si>
     <t>R+</t>
   </si>
   <si>
-    <t>r46</t>
-  </si>
-  <si>
-    <t>[R46]</t>
-  </si>
-  <si>
     <t>Mener une analyse de risques afin d'évaluer la pertinence de l'utilisation d'interphone ou de visiophone IP en dehors de la zone contrôlée. Au terme de cette analyse, si l'entité accepte les risques introduits par l'usage de technologies IP, alors l'installation d'interphone ou de visiophone IP devra se faire en cohérence avec les recommandations suivantes (cf. 6.9)</t>
   </si>
   <si>
-    <t>r47</t>
-  </si>
-  <si>
-    <t>[R47]</t>
-  </si>
-  <si>
     <t>Il est recommandé de mettre en place un moyen de détecter une tentative d'intrusion physique sur la platine de l'interphone ou du visiophone afin de se prémunir d'un accès illégitime au réseau support.</t>
   </si>
   <si>
-    <t>r48</t>
-  </si>
-  <si>
-    <t>[R48]</t>
-  </si>
-  <si>
     <t>Il est recommandé de couper immédiatement l'alimentation électrique et la connexion au réseau support en cas de tentative d'intrusion physique sur la platine de l'interphone ou du visiophone afin de se prémunir d'un accès illégitime au réseau support.</t>
   </si>
   <si>
-    <t>r49</t>
-  </si>
-  <si>
-    <t>[R49]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de s'assurer que l'interphone ou le visiophone ne crée pas de liaison entre deux réseaux distincts. Cette situation affaiblirait fortement le cloisonnement réseau (cf. 4.3.1).</t>
   </si>
   <si>
@@ -786,132 +462,51 @@
     <t>7.1</t>
   </si>
   <si>
-    <t>r50</t>
-  </si>
-  <si>
-    <t>[R50]</t>
-  </si>
-  <si>
     <t>Les flux émis et reçus par les caméras (multimédia, administration) doivent être chiffrés, intègres et authentifiés par des protocoles tels que TLS [[13]](https://cyber.gouv.fr/guide-tls) ou IPsec [[8]](https://cyber.gouv.fr/guide-ipsec).</t>
   </si>
   <si>
-    <t>r51</t>
-  </si>
-  <si>
-    <t>[R51]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de désactiver les interfaces locales d'administration des caméras déployées, lorsque de telles interfaces existent.</t>
   </si>
   <si>
-    <t>r52</t>
-  </si>
-  <si>
-    <t>[R52]</t>
-  </si>
-  <si>
     <t>Les mots de passe des caméras doivent être configurés ou remplacés par des mots de passe spécifiques, robustes et différents pour chaque équipement. Il est recommandé de mettre en place un processus de renouvellement des mots de passe. Des recommandations de sécurité relatives aux mots de passe sont décrites dans un guide de l'ANSSI consacré à ce sujet [[23]](https://cyber.gouv.fr/guide-authentification).</t>
   </si>
   <si>
-    <t>r53</t>
-  </si>
-  <si>
-    <t>[R53]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de remplacer les certificats [[13]](https://cyber.gouv.fr/guide-tls) installés par défaut dans les caméras par des certificats générés par une infrastructure de gestion de clés maîtrisée par l'entité, et dédiée au système de vidéoprotection (cf. R65).</t>
   </si>
   <si>
-    <t>r54</t>
-  </si>
-  <si>
-    <t>[R54]</t>
-  </si>
-  <si>
     <t>De manière générale, il est recommandé de désactiver les fonctions qui ne sont pas réellement utilisées dans le cadre du déploiement considéré.</t>
   </si>
   <si>
-    <t>r55</t>
-  </si>
-  <si>
-    <t>[R55]</t>
-  </si>
-  <si>
     <t>7.2</t>
   </si>
   <si>
     <t>r56p</t>
   </si>
   <si>
-    <t>[R56+]</t>
-  </si>
-  <si>
     <t>L'emploi de technologies différentes au sein des réseaux de vidéoprotection de la zone contrôlée et non contrôlée apporte une sécurité supplémentaire, en limitant les risques de voir une même vulnérabilité exploitée sur les deux réseaux. Il est recommandé de privilégier l'usage de technologies analogiques pour les caméras situées à l'extérieur de la zone contrôlée.</t>
   </si>
   <si>
-    <t>r56</t>
-  </si>
-  <si>
-    <t>[R56]</t>
-  </si>
-  <si>
     <t>Mener une analyse de risques afin d'évaluer la pertinence de l'utilisation de caméra IP en dehors de la zone contrôlée. Au terme de cette analyse, si l'entité accepte les risques introduits par l'usage de technologies IP, alors l'installation de caméra IP devra se faire en cohérence avec les recommandations suivantes (cf. 7.2).</t>
   </si>
   <si>
-    <t>r57</t>
-  </si>
-  <si>
-    <t>[R57]</t>
-  </si>
-  <si>
     <t>Lors de l'usage de caméras analogiques, il est fortement recommandé que les boîtiers de conversion analogiques-IP soient placés à l'intérieur de la zone contrôlée, à l'abri de tout accès frauduleux (à l'instar de la recommandation R38 sur l'emplacement des UTL).</t>
   </si>
   <si>
-    <t>r58</t>
-  </si>
-  <si>
-    <t>[R58]</t>
-  </si>
-  <si>
     <t>Il est recommandé que les caméras soient situées sur un point haut ou protégées par un caisson &lt;abbr title="L&amp;#x27;ajout d&amp;#x27;un caisson n&amp;#x27;est pas nécessaire si la caméra s&amp;#x27;autoprotège par conception."&gt;&lt;sup&gt;36&lt;/sup&gt;&lt;/abbr&gt;, à l'abri de tout accès frauduleux. De plus, la connexion de la caméra au réseau devrait se faire à l'intérieur de ce caisson afin de se prémunir de sa déconnexion du réseau.</t>
   </si>
   <si>
-    <t>r59</t>
-  </si>
-  <si>
-    <t>[R59]</t>
-  </si>
-  <si>
     <t>Il est recommandé de superviser l'ouverture du caisson ou du boîtier et de remonter une alarme à un opérateur, par exemple au travers du VMS.</t>
   </si>
   <si>
-    <t>r60</t>
-  </si>
-  <si>
-    <t>[R60]</t>
-  </si>
-  <si>
     <t>Il est recommandé d'appliquer le principe de surveillance croisée qui implique que chaque caméra est dans le champ de vision d'au moins une autre caméra du système. Cette approche vise à éliminer les angles morts et à réduire les risques de sabotage ou de manipulation des caméras isolées.</t>
   </si>
   <si>
-    <t>r61</t>
-  </si>
-  <si>
-    <t>[R61]</t>
-  </si>
-  <si>
     <t>Il est recommandé d'activer les fonctions de détection d'obstruction du champ si elles sont disponibles sur la caméra ou sur le VMS afin de s'assurer que la caméra extérieure est toujours opérationnelle.</t>
   </si>
   <si>
     <t>7.3</t>
   </si>
   <si>
-    <t>r62</t>
-  </si>
-  <si>
-    <t>[R62]</t>
-  </si>
-  <si>
     <t>Le SI de vidéoprotection doit être considéré comme un SI à part entière. À ce titre, il est primordial de rappeler la nécessité de sécuriser l'ensemble des éléments constituant ce SI. Il est fortement recommandé d'appliquer strictement les règles classiques d'hygiène informatique telles que décrites dans le guide de l'ANSSI consacré à ce sujet [[4]](https://cyber.gouv.fr/hygiene-informatique).</t>
   </si>
   <si>
@@ -921,45 +516,21 @@
     <t>8.1</t>
   </si>
   <si>
-    <t>r63</t>
-  </si>
-  <si>
-    <t>[R63]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de synchroniser à l'aide du protocole NTP les horloges de tous les équipements qui composent les systèmes d'information de contrôle d'accès physique et de vidéoprotection depuis une source de temps fiable. Dans le cas où les informations issues d'un système de contrôle d'accès physique sont croisées avec celles d'autres systèmes de contrôle d'accès physique ou de vidéoprotection, les sources de temps de ces systèmes doivent être synchronisées.</t>
   </si>
   <si>
     <t>8.2</t>
   </si>
   <si>
-    <t>r64</t>
-  </si>
-  <si>
-    <t>[R64]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de mener une réflexion sur le niveau de continuité de service souhaité et réalisable d'un système de contrôle d'accès physique ou de vidéoprotection.</t>
   </si>
   <si>
     <t>8.4</t>
   </si>
   <si>
-    <t>r65</t>
-  </si>
-  <si>
-    <t>[R65]</t>
-  </si>
-  <si>
     <t>La mise en place d'une ou plusieurs infrastructures de gestion de clés est recommandée, dans la mesure où cela facilite la gestion des certificats utilisés par les systèmes de contrôle d'accès physiques ou de vidéoprotection. Il est préconisé de dédier des sous-AC &lt;abbr title="Autorité de certification subordonnée."&gt;&lt;sup&gt;37&lt;/sup&gt;&lt;/abbr&gt; pour chaque système dans le cas de mutualisation d'une infrastructure de gestion de clés entre un système de contrôle d'accès physique et un système de vidéoprotection. Cette recommandation s'applique également dans le cas de mutualisation d'une infrastructure de gestion de clés pour plusieurs systèmes de contrôle d'accès physique dont le niveau de protection attendu est différent.</t>
   </si>
   <si>
-    <t>r66</t>
-  </si>
-  <si>
-    <t>[R66]</t>
-  </si>
-  <si>
     <t>Les autorités de certification de l'infrastructure de gestion de clés doivent être accessibles par tous les dispositifs utilisant des certificats délivrés par ces autorités, et ce quelle que soit la localisation de ces dispositifs.</t>
   </si>
   <si>
@@ -969,120 +540,57 @@
     <t>9.1</t>
   </si>
   <si>
-    <t>r67</t>
-  </si>
-  <si>
-    <t>[R67]</t>
-  </si>
-  <si>
     <t>Il est recommandé que la mise en oeuvre des mécanismes cryptographiques appliqués aux mécanismes d'identification et d'authentification des badges soient conformes aux règles décrites dans l'annexe B1 du référentiel général de sécurité [[20]](https://cyber.gouv.fr/rgs).</t>
   </si>
   <si>
     <t>9.1.1</t>
   </si>
   <si>
-    <t>r68</t>
-  </si>
-  <si>
-    <t>[R68]</t>
-  </si>
-  <si>
     <t>Dans la mesure du possible, il est hautement recommandé d'éviter les solutions de contrôle d'accès physique reposant uniquement sur une clé symétrique unique.</t>
   </si>
   <si>
     <t>r68m</t>
   </si>
   <si>
-    <t>[R68-]</t>
-  </si>
-  <si>
     <t>Dans le cas où l'installation d'une solution de contrôle d'accès physique reposant sur un mécanisme de clé symétrique unique est incontournable, il est fortement recommandé d'utiliser des clés symétriques distinctes en fonction du type d'utilisateur (salariés, visiteurs, etc.).</t>
   </si>
   <si>
     <t>9.1.2</t>
   </si>
   <si>
-    <t>r69</t>
-  </si>
-  <si>
-    <t>[R69]</t>
-  </si>
-  <si>
     <t>Dans le cas d'une utilisation de clés symétriques dérivées d'une clé maîtresse, il est hautement recommandé de recourir à l'utilisation d'un moduleSecure Access Module afin de protéger la clé maîtresse.</t>
   </si>
   <si>
-    <t>r70</t>
-  </si>
-  <si>
-    <t>[R70]</t>
-  </si>
-  <si>
     <t>Il est recommandé de privilégier l'usage de clés maîtresses distinctes pour chaque niveau de protection attendu des zones.</t>
   </si>
   <si>
     <t>9.1.3</t>
   </si>
   <si>
-    <t>r71</t>
-  </si>
-  <si>
-    <t>[R71]</t>
-  </si>
-  <si>
     <t>Bien qu'à la date de rédaction de ce guide, aucune solution de contrôle d'accès physique dotée d'un mécanisme d'authentification des badges reposant sur des biclés asymétriques n'ait été évaluée par l'ANSSI, il convient de privilégier ce type de solution plus flexible et plus sûr qu'une solution reposant sur des clés symétriques.</t>
   </si>
   <si>
     <t>9.2</t>
   </si>
   <si>
-    <t>r72</t>
-  </si>
-  <si>
-    <t>[R72]</t>
-  </si>
-  <si>
     <t>Afin d'assurer la protection des clés cryptographiques employées dans le système de contrôle d'accès physique, il convient d'appliquer les recommandations du référentiel général de sécurité publié par l'ANSSI [[17]](https://cyber.gouv.fr/rgs), notamment celles concernant la gestion des clés cryptographiques figurant dans l'annexe B2.</t>
   </si>
   <si>
-    <t>r73</t>
-  </si>
-  <si>
-    <t>[R73]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé qu'un événement soit enregistré dans le GAC et qu'une alerte soit générée lors de tout changement de clés d'authentification.</t>
   </si>
   <si>
-    <t>r74</t>
-  </si>
-  <si>
-    <t>[R74]</t>
-  </si>
-  <si>
     <t>La procédure de remplacement de clés cryptographiques en cas de compromission d'une clé doit être la plus transparente possible vis-à-vis des utilisateurs, et ne doit pas introduire de nouvelles failles de sécurité. Cette procédure doit être anticipée dès la phase de conception de l'architecture du système de contrôle d'accès physique, et ce quel que soit le type de clé utilisé.</t>
   </si>
   <si>
     <t>9.3</t>
   </si>
   <si>
-    <t>r75</t>
-  </si>
-  <si>
-    <t>[R75]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de privilégier les solutions s'appuyant sur des protocoles d'authentification et de chiffrement non propriétaires pour la sécurisation des flux entre les dispositifs et le centre de gestion.</t>
   </si>
   <si>
     <t>9.4</t>
   </si>
   <si>
-    <t>r76</t>
-  </si>
-  <si>
-    <t>[R76]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de privilégier des solutions de vidéoprotection proposant des protocoles standards pour le chiffrement des vidéos sauvegardées sur disque. La solution choisie doit également offrir la possibilité de s'intégrer dans une infrastructure de gestion de clés propre à l'entité (voir la section 8.4). Les algorithmes d'intégrité et de chiffrement mis en oeuvre doivent respecter les préconisations mentionnées dans le référentiel général de sécurité (RGS) [[18]](https://cyber.gouv.fr/rgs) publié par l'ANSSI.</t>
   </si>
   <si>
@@ -1092,45 +600,24 @@
     <t>10.1</t>
   </si>
   <si>
-    <t>r77</t>
-  </si>
-  <si>
-    <t>[R77]</t>
-  </si>
-  <si>
     <t>Afin de permettre d'identifier de façon univoque toute demande d'accès, un numéro d'identification unique contenu dans un badge doit être associé à chaque utilisateur.</t>
   </si>
   <si>
     <t>10.2</t>
   </si>
   <si>
-    <t>r78</t>
-  </si>
-  <si>
-    <t>[R78]</t>
-  </si>
-  <si>
     <t>Dans la mesure du possible, il est recommandé de privilégier les solutions de contrôle d'accès physique proposant une authentification multifacteur [[23]](https://cyber.gouv.fr/guide-authentification). Elles permettent à la fois l'authentification du badge et l'authentification du porteur. L'activation de cette double authentification doit être étudiée en fonction du niveau de protection attendu associé à la zone contrôlée.</t>
   </si>
   <si>
     <t>10.3</t>
   </si>
   <si>
-    <t>r79</t>
-  </si>
-  <si>
-    <t>[R79]</t>
-  </si>
-  <si>
     <t>Dans la mesure du possible, il est recommandé de privilégier une solution de contrôle d'accès physique proposant une authentification du porteur par mot de passe. En effet, le mot de passe peut être gardé secret, être modifié, et il est surtout révocable.</t>
   </si>
   <si>
     <t>r79m</t>
   </si>
   <si>
-    <t>[R79-]</t>
-  </si>
-  <si>
     <t>L'utilisation de la biométrie pour authentifier le porteur de badge dans une solution de contrôle d'accès physique est acceptable dans la mesure où les vulnérabilités de cette solution sont bien prises en compte (stockage des éléments biométriques sur le badge, révocation entraînant l'impossibilité pour le porteur de se voir affecter un nouveau badge avec les mêmes éléments biométriques).</t>
   </si>
   <si>
@@ -1143,33 +630,15 @@
     <t>10.4.1.1</t>
   </si>
   <si>
-    <t>r80</t>
-  </si>
-  <si>
-    <t>[R80]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de programmer une date de fin de validité dès la délivrance d'un badge à un collaborateur. Dans le cas d'un contrat à durée indéterminée, une date de fin de validité du badge correspondant à une durée maximum de trois ans devra être définie, programmée et renouvelée à échéance.</t>
   </si>
   <si>
-    <t>r81</t>
-  </si>
-  <si>
-    <t>[R81]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé que la gestion des badges (création, restitution) s'intègre dans le processus de gestion des ressources humaines, notamment dans les circuits d'arrivée et de départ. Les droits spécifiques du collaborateur doivent être accordés dans la mesure du possible par des responsables de validation ou par délégation à des responsables hiérarchiques, revus lors d'un changement d'affectation, et révoqués au plus tôt en cas de départ du collaborateur.</t>
   </si>
   <si>
     <t>10.4.1.2</t>
   </si>
   <si>
-    <t>r82</t>
-  </si>
-  <si>
-    <t>[R82]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de programmer une date de fin de validité dès la délivrance d'un badge à un prestataire. Dans le cas d'une mission de longue durée, une date de fin de validité du badge correspondant à une durée maximum de un an devra être définie, programmée et renouvelée si nécessaire.</t>
   </si>
   <si>
@@ -1179,45 +648,21 @@
     <t>10.4.2.1</t>
   </si>
   <si>
-    <t>r83</t>
-  </si>
-  <si>
-    <t>[R83]</t>
-  </si>
-  <si>
     <t>10.4.2.2</t>
   </si>
   <si>
-    <t>r84</t>
-  </si>
-  <si>
-    <t>[R84]</t>
-  </si>
-  <si>
     <t>Le nombre de porteurs de badge ayant des droits importants doit être réduit au strict nécessaire. Il est hautement recommandé que leur badge bénéficiant de droits importants demeure toujours à l'intérieur de la zone contrôlée. Un second badge pourra leur être attribué pour leur permettre de pénétrer dans l'enceinte puis de récupérer le badge bénéficiant de droits plus importants.</t>
   </si>
   <si>
     <t>10.4.3</t>
   </si>
   <si>
-    <t>r85</t>
-  </si>
-  <si>
-    <t>[R85]</t>
-  </si>
-  <si>
     <t>En cas de perte ou vol de son badge, le personnel concerné doit le signaler sans délai afin de faire invalider son badge. En cas d'oubli d'un badge, le personnel concerné doit le signaler sans délai afin d'invalider temporairement le badge oublié et se faire délivrer un badge d'accès provisoire.</t>
   </si>
   <si>
     <t>10.4.4</t>
   </si>
   <si>
-    <t>r86</t>
-  </si>
-  <si>
-    <t>[R86]</t>
-  </si>
-  <si>
     <t>Afin de limiter le risque de compromission d'un usage depuis un autre usage d'un même badge, il est recommandé l'emploi de cartes d'accès reposant sur une plateforme sous-jacente (ex.: Javacard) qui inclut la fonctionnalité de cloisonnement, certifiée Critères Communs avec une résistance aux attaques de niveau AV A_V AN.5.</t>
   </si>
   <si>
@@ -1227,63 +672,30 @@
     <t>11.2</t>
   </si>
   <si>
-    <t>r87</t>
-  </si>
-  <si>
-    <t>[R87]</t>
-  </si>
-  <si>
     <t>Les recommandations du guide « recommandations relatives à l'administration sécurisée des SI » [[14]](https://cyber.gouv.fr/guide-admin-si) doivent être appliquées, particulièrement celles concernant les comptes d'administration (paragraphe 7.1) qu'ils soient technique ou métier.</t>
   </si>
   <si>
     <t>11.3</t>
   </si>
   <si>
-    <t>r88</t>
-  </si>
-  <si>
-    <t>[R88]</t>
-  </si>
-  <si>
     <t>11.4</t>
   </si>
   <si>
-    <t>r89</t>
-  </si>
-  <si>
-    <t>[R89]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé d'appliquer sur les éléments d'infrastructure et les postes d'administration technique, les recommandations décrites dans le guide de l'ANSSI « Recommandations relatives à l'administration sécurisée des SI » [[14]](https://cyber.gouv.fr/guide-admin-si), incluant les particularités inhérentes à l'administration d'un SI déconnecté telles que décrites dans le chapitre 12 du guide.</t>
   </si>
   <si>
-    <t>r90</t>
-  </si>
-  <si>
-    <t>[R90]</t>
-  </si>
-  <si>
     <t>Il est recommandé d'administrer les équipements des centres de gestion de systèmes de contrôle d'accès ou de vidéoprotection depuis un réseau d'administration dédié à cet effet.</t>
   </si>
   <si>
     <t>r90m</t>
   </si>
   <si>
-    <t>[R90-]</t>
-  </si>
-  <si>
     <t>Dans le cas où la mise en place d'un réseau d'administration dédié à l'administration des centres de gestion de systèmes de contrôle d'accès ou de vidéoprotection n'est pas envisageable, il est recommandé de placer les ressources d'administration de ces systèmes dans le réseau d'administration du SI de l'entité.</t>
   </si>
   <si>
     <t>11.5</t>
   </si>
   <si>
-    <t>r91</t>
-  </si>
-  <si>
-    <t>[R91]</t>
-  </si>
-  <si>
     <t>Comme spécifié dans les recommandations R42 et R62, il est fortement recommandé d'appliquer sur les systèmes de gestion et stations de gestion, des mesures de sécurité et notamment les recommandations décrites dans le guide de l'ANSSI « La défense en profondeur appliquée aux SI » [[5]](https://cyber.gouv.fr/defense-profondeur).</t>
   </si>
   <si>
@@ -1293,42 +705,18 @@
     <t>12.2</t>
   </si>
   <si>
-    <t>r92</t>
-  </si>
-  <si>
-    <t>[R92]</t>
-  </si>
-  <si>
     <t>Dans le cadre de la maintenance globale du système de contrôle d'accès physique, la batterie de l'alimentation de secours de l'UTL doit être vérifiée au moins une fois par an &lt;abbr title="Fréquence de vérification minimum mentionnée par le CNPP dans son référentiel APSAD D83 [31]."&gt;&lt;sup&gt;43&lt;/sup&gt;&lt;/abbr&gt;. Le bon fonctionnement de cette alimentation de secours, présente dans chaque UTL, est un gage de résilience du système.</t>
   </si>
   <si>
-    <t>r93</t>
-  </si>
-  <si>
-    <t>[R93]</t>
-  </si>
-  <si>
     <t>Une attention particulière doit être portée sur les dispositifs en panne susceptibles de contenir des éléments cryptographiques. Il est recommandé, lorsque cela est possible, d'effacer voire de supprimer ces éléments cryptographiques avant envoi du dispositif pour réparation chez un prestataire. Lors d'une mise au rebut d'un dispositif, il faut s'assurer que ces éléments cryptographiques ne pourront pas être extraits. Dans le cas où ces éléments ne peuvent pas être effacés, il convient de procéder à la destruction physique du dispositif.</t>
   </si>
   <si>
-    <t>r94</t>
-  </si>
-  <si>
-    <t>[R94]</t>
-  </si>
-  <si>
     <t>Il est hautement recommandé que des sauvegardes des systèmes de gestion soient effectuées a minima hebdomadairement et journalièrement en cas d'usage intensif. Il est fortement recommandé que des tests de restauration associés soient menés régulièrement (au minimum une fois par an).</t>
   </si>
   <si>
     <t>12.3</t>
   </si>
   <si>
-    <t>r95</t>
-  </si>
-  <si>
-    <t>[R95]</t>
-  </si>
-  <si>
     <t>Il est impératif d'assurer un maintien en condition de sécurité pour les systèmes de contrôle d'accès physique et de vidéoprotection, au même titre que pour tout autre système d'information.</t>
   </si>
   <si>
@@ -1338,69 +726,33 @@
     <t>12.4.1</t>
   </si>
   <si>
-    <t>r96</t>
-  </si>
-  <si>
-    <t>[R96]</t>
-  </si>
-  <si>
     <t>Il est recommandé de privilégier les UTL disposant d'une copie de la base des droits afin d'accroître la résilience du système notamment en cas de panne sur le serveur ou logiciel de gestion du système de contrôle d'accès physique.</t>
   </si>
   <si>
     <t>12.4.3</t>
   </si>
   <si>
-    <t>r97</t>
-  </si>
-  <si>
-    <t>[R97]</t>
-  </si>
-  <si>
     <t>12.6</t>
   </si>
   <si>
-    <t>r98</t>
-  </si>
-  <si>
-    <t>[R98]</t>
-  </si>
-  <si>
     <t>Il est fortement recommandé de garder la maîtrise des secrets, par exemple les authentifiants des comptes de service, afin de ne pas nuire au bon fonctionnement du système d'information en production en cas de changement de prestataire.</t>
   </si>
   <si>
     <t>12.6.1</t>
   </si>
   <si>
-    <t>r99</t>
-  </si>
-  <si>
-    <t>[R99]</t>
-  </si>
-  <si>
     <t>Dans le cas d'un recours à une externalisation de l'administration d'une solution de contrôle d'accès physique ou de vidéoprotection, il est recommandé de se conformer à la démarche décrite dans le guide « Maîtriser les risques de l'infogéranceexternalisation des systèmes d'information » [[3]](https://cyber.gouv.fr/guide-externalisation) publié par l'ANSSI, et de recourir à un prestataire qualifié (voir la recommandation R26-). Une attention particulière doit être portée sur la mise en place de l'interconnexion entre le système de contrôle d'accès ou de vidéoprotection et le site de l'infogéreur.</t>
   </si>
   <si>
     <t>12.6.2</t>
   </si>
   <si>
-    <t>r100</t>
-  </si>
-  <si>
-    <t>[R100]</t>
-  </si>
-  <si>
     <t>Il est fortement déconseillé de mettre en place une solution de télémaintenance sur les ressources locales d'un système de contrôle d'accès physique ou de vidéoprotection, cette pratique pouvant engendrer des risques de compromission extrêmement élevés.</t>
   </si>
   <si>
     <t>12.6.3</t>
   </si>
   <si>
-    <t>r101</t>
-  </si>
-  <si>
-    <t>[R101]</t>
-  </si>
-  <si>
     <t>La mise en oeuvre de l'administration à distance d'une solution de contrôle d'accès physique ou de vidéoprotection doit respecter les règles décrites dans le chapitre 10 du guide « recommandations relatives à l'administration sécurisée des SI » [[14]](https://cyber.gouv.fr/guide-admin-si).</t>
   </si>
   <si>
@@ -1410,34 +762,16 @@
     <t>13.1</t>
   </si>
   <si>
-    <t>r102</t>
-  </si>
-  <si>
-    <t>[R102]</t>
-  </si>
-  <si>
     <t>Il convient de s'assurer que les événements métier issus des dispositifs de contrôle d'accès physique ou de vidéoprotection sont bien collectés et remontés vers le centre de gestion correspondant.</t>
   </si>
   <si>
     <t>13.2</t>
   </si>
   <si>
-    <t>r103</t>
-  </si>
-  <si>
-    <t>[R103]</t>
-  </si>
-  <si>
     <t>Une surveillance des accès et des différents rapports doit être effectuée très régulièrement afin de détecter rapidement les anomalies et les tentatives d'accès frauduleuses.</t>
   </si>
   <si>
     <t>13.3</t>
-  </si>
-  <si>
-    <t>r104</t>
-  </si>
-  <si>
-    <t>[R104]</t>
   </si>
   <si>
     <t>Il est recommandé de configurer des alertes en temps réel pour tout événement d'un niveau de criticité important.</t>
@@ -2155,6 +1489,360 @@
 * d'informations sur l'entreprise (nom, adresse) &lt;abbr title="Si des coordonnées sont indiquées sur le dos du badge pour faciliter sa restitution en cas de perte, elles ne doivent pas mentionner explicitement le nom de l&amp;#x27;entité. Mieux vaut privilégier dans ce cas l&amp;#x27;utilisation d&amp;#x27;une boîte postale."&gt;&lt;sup&gt;24&lt;/sup&gt;&lt;/abbr&gt;;
 * d'informations sur le porteur (nom, prénom, poste), en dehors de sa photo;
 * les accès autorisés. Un numéro de traçabilité peut être indiqué sur le badge à des fins administratives, mais ce numéro doit être différent du numéro d'identification. La photographie est tolérée car elle permet de vérifier rapidement que le badge appartient bien au porteur.</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R10-</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>R15-</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>R19-</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>R21-</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>R22-</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>R25</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>R26-</t>
+  </si>
+  <si>
+    <t>R27</t>
+  </si>
+  <si>
+    <t>R27-</t>
+  </si>
+  <si>
+    <t>R28</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>R29-</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>R31-</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>R34</t>
+  </si>
+  <si>
+    <t>R35</t>
+  </si>
+  <si>
+    <t>R36</t>
+  </si>
+  <si>
+    <t>R37</t>
+  </si>
+  <si>
+    <t>R38</t>
+  </si>
+  <si>
+    <t>R39</t>
+  </si>
+  <si>
+    <t>R40</t>
+  </si>
+  <si>
+    <t>R41</t>
+  </si>
+  <si>
+    <t>R42</t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>R44</t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>R46+</t>
+  </si>
+  <si>
+    <t>R46</t>
+  </si>
+  <si>
+    <t>R47</t>
+  </si>
+  <si>
+    <t>R48</t>
+  </si>
+  <si>
+    <t>R49</t>
+  </si>
+  <si>
+    <t>R50</t>
+  </si>
+  <si>
+    <t>R51</t>
+  </si>
+  <si>
+    <t>R52</t>
+  </si>
+  <si>
+    <t>R53</t>
+  </si>
+  <si>
+    <t>R54</t>
+  </si>
+  <si>
+    <t>R55</t>
+  </si>
+  <si>
+    <t>R56+</t>
+  </si>
+  <si>
+    <t>R56</t>
+  </si>
+  <si>
+    <t>R57</t>
+  </si>
+  <si>
+    <t>R58</t>
+  </si>
+  <si>
+    <t>R59</t>
+  </si>
+  <si>
+    <t>R60</t>
+  </si>
+  <si>
+    <t>R61</t>
+  </si>
+  <si>
+    <t>R62</t>
+  </si>
+  <si>
+    <t>R63</t>
+  </si>
+  <si>
+    <t>R64</t>
+  </si>
+  <si>
+    <t>R65</t>
+  </si>
+  <si>
+    <t>R66</t>
+  </si>
+  <si>
+    <t>R67</t>
+  </si>
+  <si>
+    <t>R68</t>
+  </si>
+  <si>
+    <t>R68-</t>
+  </si>
+  <si>
+    <t>R69</t>
+  </si>
+  <si>
+    <t>R70</t>
+  </si>
+  <si>
+    <t>R71</t>
+  </si>
+  <si>
+    <t>R72</t>
+  </si>
+  <si>
+    <t>R73</t>
+  </si>
+  <si>
+    <t>R74</t>
+  </si>
+  <si>
+    <t>R75</t>
+  </si>
+  <si>
+    <t>R76</t>
+  </si>
+  <si>
+    <t>R77</t>
+  </si>
+  <si>
+    <t>R78</t>
+  </si>
+  <si>
+    <t>R79</t>
+  </si>
+  <si>
+    <t>R79-</t>
+  </si>
+  <si>
+    <t>R80</t>
+  </si>
+  <si>
+    <t>R81</t>
+  </si>
+  <si>
+    <t>R82</t>
+  </si>
+  <si>
+    <t>R83</t>
+  </si>
+  <si>
+    <t>R84</t>
+  </si>
+  <si>
+    <t>R85</t>
+  </si>
+  <si>
+    <t>R86</t>
+  </si>
+  <si>
+    <t>R87</t>
+  </si>
+  <si>
+    <t>R88</t>
+  </si>
+  <si>
+    <t>R89</t>
+  </si>
+  <si>
+    <t>R90</t>
+  </si>
+  <si>
+    <t>R90-</t>
+  </si>
+  <si>
+    <t>R91</t>
+  </si>
+  <si>
+    <t>R92</t>
+  </si>
+  <si>
+    <t>R93</t>
+  </si>
+  <si>
+    <t>R94</t>
+  </si>
+  <si>
+    <t>R95</t>
+  </si>
+  <si>
+    <t>R96</t>
+  </si>
+  <si>
+    <t>R97</t>
+  </si>
+  <si>
+    <t>R98</t>
+  </si>
+  <si>
+    <t>R99</t>
+  </si>
+  <si>
+    <t>R100</t>
+  </si>
+  <si>
+    <t>R101</t>
+  </si>
+  <si>
+    <t>R102</t>
+  </si>
+  <si>
+    <t>R103</t>
+  </si>
+  <si>
+    <t>R104</t>
   </si>
 </sst>
 </file>
@@ -2588,7 +2276,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>681</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
@@ -2674,7 +2362,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>681</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -2745,7 +2433,7 @@
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>485</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -2756,7 +2444,7 @@
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>486</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -2766,23 +2454,20 @@
       <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>475</v>
       </c>
       <c r="E4" t="s">
-        <v>487</v>
+        <v>265</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>477</v>
+        <v>255</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>472</v>
+        <v>250</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -2793,7 +2478,7 @@
         <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>488</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -2801,10 +2486,10 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>489</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -2814,20 +2499,17 @@
       <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>476</v>
       </c>
       <c r="E7" t="s">
-        <v>490</v>
+        <v>268</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -2835,10 +2517,10 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>491</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2848,20 +2530,17 @@
       <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>477</v>
       </c>
       <c r="E9" t="s">
-        <v>492</v>
+        <v>270</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -2869,10 +2548,10 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>493</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2882,20 +2561,17 @@
       <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>478</v>
       </c>
       <c r="E11" t="s">
-        <v>494</v>
+        <v>272</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2905,20 +2581,17 @@
       <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>479</v>
       </c>
       <c r="E12" t="s">
-        <v>495</v>
+        <v>273</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -2926,10 +2599,10 @@
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>682</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -2939,20 +2612,17 @@
       <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>480</v>
       </c>
       <c r="E14" t="s">
-        <v>496</v>
+        <v>274</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -2960,10 +2630,10 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>497</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -2973,20 +2643,17 @@
       <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="C16" t="s">
-        <v>57</v>
-      </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>481</v>
       </c>
       <c r="E16" t="s">
-        <v>498</v>
+        <v>276</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -2994,10 +2661,10 @@
         <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>499</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3007,20 +2674,17 @@
       <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" t="s">
-        <v>61</v>
-      </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>482</v>
       </c>
       <c r="E18" t="s">
-        <v>500</v>
+        <v>278</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -3028,10 +2692,10 @@
         <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>501</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3041,20 +2705,17 @@
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" t="s">
-        <v>65</v>
-      </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>483</v>
       </c>
       <c r="E20" t="s">
-        <v>502</v>
+        <v>280</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -3062,10 +2723,10 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>503</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -3073,10 +2734,10 @@
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E22" t="s">
-        <v>504</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3086,20 +2747,17 @@
       <c r="B23" t="s">
         <v>33</v>
       </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>484</v>
       </c>
       <c r="E23" t="s">
-        <v>505</v>
+        <v>283</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3110,19 +2768,19 @@
         <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>485</v>
       </c>
       <c r="E24" t="s">
-        <v>506</v>
+        <v>284</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="H24" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3132,20 +2790,17 @@
       <c r="B25" t="s">
         <v>33</v>
       </c>
-      <c r="C25" t="s">
-        <v>77</v>
-      </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="E25" t="s">
-        <v>507</v>
+        <v>285</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -3153,10 +2808,10 @@
         <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>508</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -3164,10 +2819,10 @@
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>509</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3175,22 +2830,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="E28" t="s">
-        <v>510</v>
+        <v>288</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="H28" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -3198,10 +2850,10 @@
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E29" t="s">
-        <v>683</v>
+        <v>461</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3209,22 +2861,19 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>488</v>
       </c>
       <c r="E30" t="s">
-        <v>511</v>
+        <v>289</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -3232,22 +2881,19 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>489</v>
       </c>
       <c r="E31" t="s">
-        <v>512</v>
+        <v>290</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="H31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -3255,10 +2901,10 @@
         <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="E32" t="s">
-        <v>513</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3266,22 +2912,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>490</v>
       </c>
       <c r="E33" t="s">
-        <v>514</v>
+        <v>292</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3289,22 +2932,22 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>491</v>
       </c>
       <c r="E34" t="s">
-        <v>515</v>
+        <v>293</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H34" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -3312,10 +2955,10 @@
         <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>684</v>
+        <v>462</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -3323,10 +2966,10 @@
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>685</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3334,22 +2977,19 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>492</v>
       </c>
       <c r="E37" t="s">
-        <v>516</v>
+        <v>294</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="H37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -3357,10 +2997,10 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="E38" t="s">
-        <v>517</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3368,22 +3008,19 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>493</v>
       </c>
       <c r="E39" t="s">
-        <v>518</v>
+        <v>296</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -3391,22 +3028,19 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>494</v>
       </c>
       <c r="E40" t="s">
-        <v>519</v>
+        <v>297</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -3414,22 +3048,19 @@
         <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>495</v>
       </c>
       <c r="E41" t="s">
-        <v>520</v>
+        <v>298</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3437,22 +3068,22 @@
         <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D42" t="s">
-        <v>115</v>
+        <v>496</v>
       </c>
       <c r="E42" t="s">
-        <v>521</v>
+        <v>299</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="H42" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -3460,10 +3091,10 @@
         <v>33</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="E43" t="s">
-        <v>686</v>
+        <v>464</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3471,22 +3102,19 @@
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>497</v>
       </c>
       <c r="E44" t="s">
-        <v>522</v>
+        <v>300</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
@@ -3494,10 +3122,10 @@
         <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="E45" t="s">
-        <v>687</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -3505,22 +3133,19 @@
         <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>123</v>
+        <v>498</v>
       </c>
       <c r="E46" t="s">
-        <v>523</v>
+        <v>301</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -3528,25 +3153,25 @@
         <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>499</v>
       </c>
       <c r="E47" t="s">
-        <v>524</v>
+        <v>302</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>473</v>
+        <v>251</v>
       </c>
       <c r="H47" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -3554,10 +3179,10 @@
         <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="E48" t="s">
-        <v>688</v>
+        <v>466</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3565,22 +3190,19 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="E49" t="s">
-        <v>525</v>
+        <v>303</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3588,22 +3210,22 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>501</v>
       </c>
       <c r="E50" t="s">
-        <v>526</v>
+        <v>304</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
@@ -3611,10 +3233,10 @@
         <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="E51" t="s">
-        <v>689</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -3622,10 +3244,10 @@
         <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="E52" t="s">
-        <v>527</v>
+        <v>305</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3633,22 +3255,19 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>138</v>
+        <v>502</v>
       </c>
       <c r="E53" t="s">
-        <v>528</v>
+        <v>306</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
@@ -3656,10 +3275,10 @@
         <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>529</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -3667,22 +3286,19 @@
         <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
-      </c>
-      <c r="C55" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>503</v>
       </c>
       <c r="E55" t="s">
-        <v>530</v>
+        <v>308</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>479</v>
+        <v>257</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
@@ -3690,10 +3306,10 @@
         <v>33</v>
       </c>
       <c r="D56" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="E56" t="s">
-        <v>531</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3701,22 +3317,19 @@
         <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>504</v>
       </c>
       <c r="E57" t="s">
-        <v>532</v>
+        <v>310</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -3724,10 +3337,10 @@
         <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="E58" t="s">
-        <v>533</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -3737,20 +3350,17 @@
       <c r="B59" t="s">
         <v>33</v>
       </c>
-      <c r="C59" t="s">
-        <v>148</v>
-      </c>
       <c r="D59" t="s">
-        <v>149</v>
+        <v>505</v>
       </c>
       <c r="E59" t="s">
-        <v>534</v>
+        <v>312</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3761,22 +3371,22 @@
         <v>33</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>506</v>
       </c>
       <c r="E60" t="s">
-        <v>535</v>
+        <v>313</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>474</v>
+        <v>252</v>
       </c>
       <c r="H60" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
@@ -3784,10 +3394,10 @@
         <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="E61" t="s">
-        <v>536</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -3795,10 +3405,10 @@
         <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="E62" t="s">
-        <v>690</v>
+        <v>468</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -3806,22 +3416,19 @@
         <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>157</v>
+        <v>507</v>
       </c>
       <c r="E63" t="s">
-        <v>537</v>
+        <v>315</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="H63" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3829,22 +3436,22 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C64" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>508</v>
       </c>
       <c r="E64" t="s">
-        <v>538</v>
+        <v>316</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="H64" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -3852,25 +3459,22 @@
         <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" t="s">
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="E65" t="s">
-        <v>539</v>
+        <v>317</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>475</v>
+        <v>253</v>
       </c>
       <c r="H65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -3878,10 +3482,10 @@
         <v>33</v>
       </c>
       <c r="D66" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="E66" t="s">
-        <v>691</v>
+        <v>469</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -3889,22 +3493,19 @@
         <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" t="s">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>167</v>
+        <v>510</v>
       </c>
       <c r="E67" t="s">
-        <v>540</v>
+        <v>318</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="H67" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -3912,22 +3513,22 @@
         <v>32</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>170</v>
+        <v>511</v>
       </c>
       <c r="E68" t="s">
-        <v>541</v>
+        <v>319</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="H68" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -3935,10 +3536,10 @@
         <v>5</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="E69" t="s">
-        <v>542</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -3946,10 +3547,10 @@
         <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="E70" t="s">
-        <v>543</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -3959,20 +3560,17 @@
       <c r="B71" t="s">
         <v>33</v>
       </c>
-      <c r="C71" t="s">
-        <v>174</v>
-      </c>
       <c r="D71" t="s">
-        <v>175</v>
+        <v>512</v>
       </c>
       <c r="E71" t="s">
-        <v>544</v>
+        <v>322</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>480</v>
+        <v>258</v>
       </c>
       <c r="H71" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -3980,10 +3578,10 @@
         <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="E72" t="s">
-        <v>545</v>
+        <v>323</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -3991,10 +3589,10 @@
         <v>30</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="E73" t="s">
-        <v>692</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -4004,23 +3602,20 @@
       <c r="B74" t="s">
         <v>33</v>
       </c>
-      <c r="C74" t="s">
-        <v>178</v>
-      </c>
       <c r="D74" t="s">
-        <v>179</v>
+        <v>513</v>
       </c>
       <c r="E74" t="s">
-        <v>546</v>
+        <v>324</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>478</v>
+        <v>256</v>
       </c>
       <c r="H74" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4031,19 +3626,19 @@
         <v>33</v>
       </c>
       <c r="C75" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="D75" t="s">
-        <v>182</v>
+        <v>514</v>
       </c>
       <c r="E75" t="s">
-        <v>547</v>
+        <v>325</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="H75" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -4053,20 +3648,17 @@
       <c r="B76" t="s">
         <v>33</v>
       </c>
-      <c r="C76" t="s">
-        <v>184</v>
-      </c>
       <c r="D76" t="s">
-        <v>185</v>
+        <v>515</v>
       </c>
       <c r="E76" t="s">
-        <v>548</v>
+        <v>326</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>696</v>
+        <v>474</v>
       </c>
       <c r="H76" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4076,20 +3668,17 @@
       <c r="B77" t="s">
         <v>33</v>
       </c>
-      <c r="C77" t="s">
-        <v>186</v>
-      </c>
       <c r="D77" t="s">
-        <v>187</v>
+        <v>516</v>
       </c>
       <c r="E77" t="s">
-        <v>549</v>
+        <v>327</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="H77" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4099,20 +3688,17 @@
       <c r="B78" t="s">
         <v>33</v>
       </c>
-      <c r="C78" t="s">
-        <v>189</v>
-      </c>
       <c r="D78" t="s">
-        <v>190</v>
+        <v>517</v>
       </c>
       <c r="E78" t="s">
-        <v>550</v>
+        <v>328</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="H78" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
@@ -4120,10 +3706,10 @@
         <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>192</v>
+        <v>115</v>
       </c>
       <c r="E79" t="s">
-        <v>693</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4133,20 +3719,17 @@
       <c r="B80" t="s">
         <v>33</v>
       </c>
-      <c r="C80" t="s">
-        <v>193</v>
-      </c>
       <c r="D80" t="s">
-        <v>194</v>
+        <v>518</v>
       </c>
       <c r="E80" t="s">
-        <v>551</v>
+        <v>329</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="H80" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
@@ -4154,10 +3737,10 @@
         <v>30</v>
       </c>
       <c r="D81" t="s">
-        <v>196</v>
+        <v>117</v>
       </c>
       <c r="E81" t="s">
-        <v>552</v>
+        <v>330</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4167,20 +3750,17 @@
       <c r="B82" t="s">
         <v>33</v>
       </c>
-      <c r="C82" t="s">
-        <v>197</v>
-      </c>
       <c r="D82" t="s">
-        <v>198</v>
+        <v>519</v>
       </c>
       <c r="E82" t="s">
-        <v>553</v>
+        <v>331</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="H82" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4190,20 +3770,17 @@
       <c r="B83" t="s">
         <v>33</v>
       </c>
-      <c r="C83" t="s">
-        <v>200</v>
-      </c>
       <c r="D83" t="s">
-        <v>201</v>
+        <v>520</v>
       </c>
       <c r="E83" t="s">
-        <v>554</v>
+        <v>332</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>202</v>
+        <v>119</v>
       </c>
       <c r="H83" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -4211,10 +3788,10 @@
         <v>30</v>
       </c>
       <c r="D84" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="E84" t="s">
-        <v>555</v>
+        <v>333</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4224,20 +3801,17 @@
       <c r="B85" t="s">
         <v>33</v>
       </c>
-      <c r="C85" t="s">
-        <v>204</v>
-      </c>
       <c r="D85" t="s">
-        <v>205</v>
+        <v>521</v>
       </c>
       <c r="E85" t="s">
-        <v>556</v>
+        <v>334</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c r="H85" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4247,20 +3821,17 @@
       <c r="B86" t="s">
         <v>33</v>
       </c>
-      <c r="C86" t="s">
-        <v>207</v>
-      </c>
       <c r="D86" t="s">
-        <v>208</v>
+        <v>522</v>
       </c>
       <c r="E86" t="s">
-        <v>557</v>
+        <v>335</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="H86" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4270,20 +3841,17 @@
       <c r="B87" t="s">
         <v>33</v>
       </c>
-      <c r="C87" t="s">
-        <v>210</v>
-      </c>
       <c r="D87" t="s">
-        <v>211</v>
+        <v>523</v>
       </c>
       <c r="E87" t="s">
-        <v>558</v>
+        <v>336</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>212</v>
+        <v>123</v>
       </c>
       <c r="H87" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
@@ -4291,10 +3859,10 @@
         <v>30</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
       <c r="E88" t="s">
-        <v>559</v>
+        <v>337</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -4304,20 +3872,17 @@
       <c r="B89" t="s">
         <v>33</v>
       </c>
-      <c r="C89" t="s">
-        <v>214</v>
-      </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>524</v>
       </c>
       <c r="E89" t="s">
-        <v>560</v>
+        <v>338</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="H89" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -4325,10 +3890,10 @@
         <v>30</v>
       </c>
       <c r="D90" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="E90" t="s">
-        <v>561</v>
+        <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4338,20 +3903,17 @@
       <c r="B91" t="s">
         <v>33</v>
       </c>
-      <c r="C91" t="s">
-        <v>218</v>
-      </c>
       <c r="D91" t="s">
-        <v>219</v>
+        <v>525</v>
       </c>
       <c r="E91" t="s">
-        <v>562</v>
+        <v>340</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="H91" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -4359,10 +3921,10 @@
         <v>30</v>
       </c>
       <c r="D92" t="s">
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="E92" t="s">
-        <v>563</v>
+        <v>341</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4372,20 +3934,17 @@
       <c r="B93" t="s">
         <v>33</v>
       </c>
-      <c r="C93" t="s">
-        <v>222</v>
-      </c>
       <c r="D93" t="s">
-        <v>223</v>
+        <v>526</v>
       </c>
       <c r="E93" t="s">
-        <v>564</v>
+        <v>342</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>224</v>
+        <v>129</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4395,20 +3954,17 @@
       <c r="B94" t="s">
         <v>33</v>
       </c>
-      <c r="C94" t="s">
-        <v>225</v>
-      </c>
       <c r="D94" t="s">
-        <v>226</v>
+        <v>527</v>
       </c>
       <c r="E94" t="s">
-        <v>565</v>
+        <v>343</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>227</v>
+        <v>130</v>
       </c>
       <c r="H94" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -4416,10 +3972,10 @@
         <v>30</v>
       </c>
       <c r="D95" t="s">
-        <v>228</v>
+        <v>131</v>
       </c>
       <c r="E95" t="s">
-        <v>566</v>
+        <v>344</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4429,20 +3985,17 @@
       <c r="B96" t="s">
         <v>33</v>
       </c>
-      <c r="C96" t="s">
-        <v>229</v>
-      </c>
       <c r="D96" t="s">
-        <v>230</v>
+        <v>528</v>
       </c>
       <c r="E96" t="s">
-        <v>567</v>
+        <v>345</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>231</v>
+        <v>132</v>
       </c>
       <c r="H96" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4453,19 +4006,19 @@
         <v>33</v>
       </c>
       <c r="C97" t="s">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="D97" t="s">
-        <v>233</v>
+        <v>529</v>
       </c>
       <c r="E97" t="s">
-        <v>568</v>
+        <v>346</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>234</v>
+        <v>134</v>
       </c>
       <c r="H97" t="s">
-        <v>235</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4475,23 +4028,20 @@
       <c r="B98" t="s">
         <v>33</v>
       </c>
-      <c r="C98" t="s">
-        <v>236</v>
-      </c>
       <c r="D98" t="s">
-        <v>237</v>
+        <v>530</v>
       </c>
       <c r="E98" t="s">
-        <v>569</v>
+        <v>347</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>238</v>
+        <v>136</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>476</v>
+        <v>254</v>
       </c>
       <c r="H98" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4501,20 +4051,17 @@
       <c r="B99" t="s">
         <v>33</v>
       </c>
-      <c r="C99" t="s">
-        <v>239</v>
-      </c>
       <c r="D99" t="s">
-        <v>240</v>
+        <v>531</v>
       </c>
       <c r="E99" t="s">
-        <v>570</v>
+        <v>348</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>241</v>
+        <v>137</v>
       </c>
       <c r="H99" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4524,20 +4071,17 @@
       <c r="B100" t="s">
         <v>33</v>
       </c>
-      <c r="C100" t="s">
-        <v>242</v>
-      </c>
       <c r="D100" t="s">
-        <v>243</v>
+        <v>532</v>
       </c>
       <c r="E100" t="s">
-        <v>695</v>
+        <v>473</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>244</v>
+        <v>138</v>
       </c>
       <c r="H100" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4547,20 +4091,17 @@
       <c r="B101" t="s">
         <v>33</v>
       </c>
-      <c r="C101" t="s">
-        <v>245</v>
-      </c>
       <c r="D101" t="s">
-        <v>246</v>
+        <v>533</v>
       </c>
       <c r="E101" t="s">
-        <v>571</v>
+        <v>349</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>247</v>
+        <v>139</v>
       </c>
       <c r="H101" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
@@ -4568,10 +4109,10 @@
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>248</v>
+        <v>140</v>
       </c>
       <c r="E102" t="s">
-        <v>572</v>
+        <v>350</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -4579,10 +4120,10 @@
         <v>30</v>
       </c>
       <c r="D103" t="s">
-        <v>249</v>
+        <v>141</v>
       </c>
       <c r="E103" t="s">
-        <v>573</v>
+        <v>351</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4592,20 +4133,17 @@
       <c r="B104" t="s">
         <v>33</v>
       </c>
-      <c r="C104" t="s">
-        <v>250</v>
-      </c>
       <c r="D104" t="s">
-        <v>251</v>
+        <v>534</v>
       </c>
       <c r="E104" t="s">
-        <v>574</v>
+        <v>352</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>252</v>
+        <v>142</v>
       </c>
       <c r="H104" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
@@ -4615,20 +4153,17 @@
       <c r="B105" t="s">
         <v>33</v>
       </c>
-      <c r="C105" t="s">
-        <v>253</v>
-      </c>
       <c r="D105" t="s">
-        <v>254</v>
+        <v>535</v>
       </c>
       <c r="E105" t="s">
-        <v>575</v>
+        <v>353</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>255</v>
+        <v>143</v>
       </c>
       <c r="H105" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4638,20 +4173,17 @@
       <c r="B106" t="s">
         <v>33</v>
       </c>
-      <c r="C106" t="s">
-        <v>256</v>
-      </c>
       <c r="D106" t="s">
-        <v>257</v>
+        <v>536</v>
       </c>
       <c r="E106" t="s">
-        <v>576</v>
+        <v>354</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>258</v>
+        <v>144</v>
       </c>
       <c r="H106" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4661,20 +4193,17 @@
       <c r="B107" t="s">
         <v>33</v>
       </c>
-      <c r="C107" t="s">
-        <v>259</v>
-      </c>
       <c r="D107" t="s">
-        <v>260</v>
+        <v>537</v>
       </c>
       <c r="E107" t="s">
-        <v>577</v>
+        <v>355</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>261</v>
+        <v>145</v>
       </c>
       <c r="H107" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
@@ -4684,20 +4213,17 @@
       <c r="B108" t="s">
         <v>33</v>
       </c>
-      <c r="C108" t="s">
-        <v>262</v>
-      </c>
       <c r="D108" t="s">
-        <v>263</v>
+        <v>538</v>
       </c>
       <c r="E108" t="s">
-        <v>578</v>
+        <v>356</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>264</v>
+        <v>146</v>
       </c>
       <c r="H108" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4707,20 +4233,17 @@
       <c r="B109" t="s">
         <v>33</v>
       </c>
-      <c r="C109" t="s">
-        <v>265</v>
-      </c>
       <c r="D109" t="s">
-        <v>266</v>
+        <v>539</v>
       </c>
       <c r="E109" t="s">
-        <v>579</v>
+        <v>357</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>481</v>
+        <v>259</v>
       </c>
       <c r="H109" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
@@ -4728,10 +4251,10 @@
         <v>30</v>
       </c>
       <c r="D110" t="s">
-        <v>267</v>
+        <v>147</v>
       </c>
       <c r="E110" t="s">
-        <v>580</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4742,19 +4265,19 @@
         <v>33</v>
       </c>
       <c r="C111" t="s">
-        <v>268</v>
+        <v>148</v>
       </c>
       <c r="D111" t="s">
-        <v>269</v>
+        <v>540</v>
       </c>
       <c r="E111" t="s">
-        <v>581</v>
+        <v>359</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>270</v>
+        <v>149</v>
       </c>
       <c r="H111" t="s">
-        <v>235</v>
+        <v>135</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4764,20 +4287,17 @@
       <c r="B112" t="s">
         <v>33</v>
       </c>
-      <c r="C112" t="s">
-        <v>271</v>
-      </c>
       <c r="D112" t="s">
-        <v>272</v>
+        <v>541</v>
       </c>
       <c r="E112" t="s">
-        <v>582</v>
+        <v>360</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>273</v>
+        <v>150</v>
       </c>
       <c r="H112" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4787,23 +4307,20 @@
       <c r="B113" t="s">
         <v>33</v>
       </c>
-      <c r="C113" t="s">
-        <v>274</v>
-      </c>
       <c r="D113" t="s">
-        <v>275</v>
+        <v>542</v>
       </c>
       <c r="E113" t="s">
-        <v>583</v>
+        <v>361</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>276</v>
+        <v>151</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>476</v>
+        <v>254</v>
       </c>
       <c r="H113" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4813,20 +4330,17 @@
       <c r="B114" t="s">
         <v>33</v>
       </c>
-      <c r="C114" t="s">
-        <v>277</v>
-      </c>
       <c r="D114" t="s">
-        <v>278</v>
+        <v>543</v>
       </c>
       <c r="E114" t="s">
-        <v>584</v>
+        <v>362</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="H114" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
@@ -4836,20 +4350,17 @@
       <c r="B115" t="s">
         <v>33</v>
       </c>
-      <c r="C115" t="s">
-        <v>280</v>
-      </c>
       <c r="D115" t="s">
-        <v>281</v>
+        <v>544</v>
       </c>
       <c r="E115" t="s">
-        <v>585</v>
+        <v>363</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>282</v>
+        <v>153</v>
       </c>
       <c r="H115" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4859,20 +4370,17 @@
       <c r="B116" t="s">
         <v>33</v>
       </c>
-      <c r="C116" t="s">
-        <v>283</v>
-      </c>
       <c r="D116" t="s">
-        <v>284</v>
+        <v>545</v>
       </c>
       <c r="E116" t="s">
-        <v>586</v>
+        <v>364</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>285</v>
+        <v>154</v>
       </c>
       <c r="H116" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4882,20 +4390,17 @@
       <c r="B117" t="s">
         <v>33</v>
       </c>
-      <c r="C117" t="s">
-        <v>286</v>
-      </c>
       <c r="D117" t="s">
-        <v>287</v>
+        <v>546</v>
       </c>
       <c r="E117" t="s">
-        <v>587</v>
+        <v>365</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>288</v>
+        <v>155</v>
       </c>
       <c r="H117" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
@@ -4903,10 +4408,10 @@
         <v>30</v>
       </c>
       <c r="D118" t="s">
-        <v>289</v>
+        <v>156</v>
       </c>
       <c r="E118" t="s">
-        <v>588</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4916,20 +4421,17 @@
       <c r="B119" t="s">
         <v>33</v>
       </c>
-      <c r="C119" t="s">
-        <v>290</v>
-      </c>
       <c r="D119" t="s">
-        <v>291</v>
+        <v>547</v>
       </c>
       <c r="E119" t="s">
-        <v>589</v>
+        <v>367</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>292</v>
+        <v>157</v>
       </c>
       <c r="H119" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
@@ -4937,10 +4439,10 @@
         <v>5</v>
       </c>
       <c r="D120" t="s">
-        <v>293</v>
+        <v>158</v>
       </c>
       <c r="E120" t="s">
-        <v>590</v>
+        <v>368</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
@@ -4948,10 +4450,10 @@
         <v>30</v>
       </c>
       <c r="D121" t="s">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c r="E121" t="s">
-        <v>591</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4961,20 +4463,17 @@
       <c r="B122" t="s">
         <v>33</v>
       </c>
-      <c r="C122" t="s">
-        <v>295</v>
-      </c>
       <c r="D122" t="s">
-        <v>296</v>
+        <v>548</v>
       </c>
       <c r="E122" t="s">
-        <v>592</v>
+        <v>370</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>297</v>
+        <v>160</v>
       </c>
       <c r="H122" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
@@ -4982,10 +4481,10 @@
         <v>30</v>
       </c>
       <c r="D123" t="s">
-        <v>298</v>
+        <v>161</v>
       </c>
       <c r="E123" t="s">
-        <v>593</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4995,20 +4494,17 @@
       <c r="B124" t="s">
         <v>33</v>
       </c>
-      <c r="C124" t="s">
-        <v>299</v>
-      </c>
       <c r="D124" t="s">
-        <v>300</v>
+        <v>549</v>
       </c>
       <c r="E124" t="s">
-        <v>594</v>
+        <v>372</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>301</v>
+        <v>162</v>
       </c>
       <c r="H124" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
@@ -5016,10 +4512,10 @@
         <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>302</v>
+        <v>163</v>
       </c>
       <c r="E125" t="s">
-        <v>595</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5029,20 +4525,17 @@
       <c r="B126" t="s">
         <v>33</v>
       </c>
-      <c r="C126" t="s">
-        <v>303</v>
-      </c>
       <c r="D126" t="s">
-        <v>304</v>
+        <v>550</v>
       </c>
       <c r="E126" t="s">
-        <v>596</v>
+        <v>374</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>305</v>
+        <v>164</v>
       </c>
       <c r="H126" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5052,20 +4545,17 @@
       <c r="B127" t="s">
         <v>33</v>
       </c>
-      <c r="C127" t="s">
-        <v>306</v>
-      </c>
       <c r="D127" t="s">
-        <v>307</v>
+        <v>551</v>
       </c>
       <c r="E127" t="s">
-        <v>597</v>
+        <v>375</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>308</v>
+        <v>165</v>
       </c>
       <c r="H127" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
@@ -5073,10 +4563,10 @@
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>309</v>
+        <v>166</v>
       </c>
       <c r="E128" t="s">
-        <v>598</v>
+        <v>376</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
@@ -5084,10 +4574,10 @@
         <v>30</v>
       </c>
       <c r="D129" t="s">
-        <v>310</v>
+        <v>167</v>
       </c>
       <c r="E129" t="s">
-        <v>599</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5097,20 +4587,17 @@
       <c r="B130" t="s">
         <v>33</v>
       </c>
-      <c r="C130" t="s">
-        <v>311</v>
-      </c>
       <c r="D130" t="s">
-        <v>312</v>
+        <v>552</v>
       </c>
       <c r="E130" t="s">
-        <v>600</v>
+        <v>378</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>313</v>
+        <v>168</v>
       </c>
       <c r="H130" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
@@ -5118,10 +4605,10 @@
         <v>33</v>
       </c>
       <c r="D131" t="s">
-        <v>314</v>
+        <v>169</v>
       </c>
       <c r="E131" t="s">
-        <v>601</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
@@ -5129,22 +4616,19 @@
         <v>32</v>
       </c>
       <c r="B132" t="s">
-        <v>68</v>
-      </c>
-      <c r="C132" t="s">
-        <v>315</v>
+        <v>50</v>
       </c>
       <c r="D132" t="s">
-        <v>316</v>
+        <v>553</v>
       </c>
       <c r="E132" t="s">
-        <v>602</v>
+        <v>380</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>317</v>
+        <v>170</v>
       </c>
       <c r="H132" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5152,22 +4636,22 @@
         <v>32</v>
       </c>
       <c r="B133" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C133" t="s">
-        <v>318</v>
+        <v>171</v>
       </c>
       <c r="D133" t="s">
-        <v>319</v>
+        <v>554</v>
       </c>
       <c r="E133" t="s">
-        <v>603</v>
+        <v>381</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>320</v>
+        <v>172</v>
       </c>
       <c r="H133" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
@@ -5175,10 +4659,10 @@
         <v>33</v>
       </c>
       <c r="D134" t="s">
-        <v>321</v>
+        <v>173</v>
       </c>
       <c r="E134" t="s">
-        <v>604</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5186,22 +4670,19 @@
         <v>32</v>
       </c>
       <c r="B135" t="s">
-        <v>68</v>
-      </c>
-      <c r="C135" t="s">
-        <v>322</v>
+        <v>50</v>
       </c>
       <c r="D135" t="s">
-        <v>323</v>
+        <v>555</v>
       </c>
       <c r="E135" t="s">
-        <v>605</v>
+        <v>383</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>324</v>
+        <v>174</v>
       </c>
       <c r="H135" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
@@ -5209,22 +4690,19 @@
         <v>32</v>
       </c>
       <c r="B136" t="s">
-        <v>68</v>
-      </c>
-      <c r="C136" t="s">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="D136" t="s">
-        <v>326</v>
+        <v>556</v>
       </c>
       <c r="E136" t="s">
-        <v>606</v>
+        <v>384</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>327</v>
+        <v>175</v>
       </c>
       <c r="H136" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
@@ -5232,10 +4710,10 @@
         <v>33</v>
       </c>
       <c r="D137" t="s">
-        <v>328</v>
+        <v>176</v>
       </c>
       <c r="E137" t="s">
-        <v>607</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5243,22 +4721,19 @@
         <v>32</v>
       </c>
       <c r="B138" t="s">
-        <v>68</v>
-      </c>
-      <c r="C138" t="s">
-        <v>329</v>
+        <v>50</v>
       </c>
       <c r="D138" t="s">
-        <v>330</v>
+        <v>557</v>
       </c>
       <c r="E138" t="s">
-        <v>608</v>
+        <v>386</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>331</v>
+        <v>177</v>
       </c>
       <c r="H138" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
@@ -5266,10 +4741,10 @@
         <v>30</v>
       </c>
       <c r="D139" t="s">
-        <v>332</v>
+        <v>178</v>
       </c>
       <c r="E139" t="s">
-        <v>609</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5279,20 +4754,17 @@
       <c r="B140" t="s">
         <v>33</v>
       </c>
-      <c r="C140" t="s">
-        <v>333</v>
-      </c>
       <c r="D140" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="E140" t="s">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>335</v>
+        <v>179</v>
       </c>
       <c r="H140" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
@@ -5302,20 +4774,17 @@
       <c r="B141" t="s">
         <v>33</v>
       </c>
-      <c r="C141" t="s">
-        <v>336</v>
-      </c>
       <c r="D141" t="s">
-        <v>337</v>
+        <v>559</v>
       </c>
       <c r="E141" t="s">
-        <v>611</v>
+        <v>389</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>338</v>
+        <v>180</v>
       </c>
       <c r="H141" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5325,20 +4794,17 @@
       <c r="B142" t="s">
         <v>33</v>
       </c>
-      <c r="C142" t="s">
-        <v>339</v>
-      </c>
       <c r="D142" t="s">
-        <v>340</v>
+        <v>560</v>
       </c>
       <c r="E142" t="s">
-        <v>612</v>
+        <v>390</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>341</v>
+        <v>181</v>
       </c>
       <c r="H142" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
@@ -5346,10 +4812,10 @@
         <v>30</v>
       </c>
       <c r="D143" t="s">
-        <v>342</v>
+        <v>182</v>
       </c>
       <c r="E143" t="s">
-        <v>694</v>
+        <v>472</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5359,20 +4825,17 @@
       <c r="B144" t="s">
         <v>33</v>
       </c>
-      <c r="C144" t="s">
-        <v>343</v>
-      </c>
       <c r="D144" t="s">
-        <v>344</v>
+        <v>561</v>
       </c>
       <c r="E144" t="s">
-        <v>613</v>
+        <v>391</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>345</v>
+        <v>183</v>
       </c>
       <c r="H144" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
@@ -5380,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="D145" t="s">
-        <v>346</v>
+        <v>184</v>
       </c>
       <c r="E145" t="s">
-        <v>614</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -5393,20 +4856,17 @@
       <c r="B146" t="s">
         <v>33</v>
       </c>
-      <c r="C146" t="s">
-        <v>347</v>
-      </c>
       <c r="D146" t="s">
-        <v>348</v>
+        <v>562</v>
       </c>
       <c r="E146" t="s">
-        <v>615</v>
+        <v>393</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>349</v>
+        <v>185</v>
       </c>
       <c r="H146" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
@@ -5414,10 +4874,10 @@
         <v>5</v>
       </c>
       <c r="D147" t="s">
-        <v>350</v>
+        <v>186</v>
       </c>
       <c r="E147" t="s">
-        <v>616</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
@@ -5425,10 +4885,10 @@
         <v>30</v>
       </c>
       <c r="D148" t="s">
-        <v>351</v>
+        <v>187</v>
       </c>
       <c r="E148" t="s">
-        <v>617</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5438,20 +4898,17 @@
       <c r="B149" t="s">
         <v>33</v>
       </c>
-      <c r="C149" t="s">
-        <v>352</v>
-      </c>
       <c r="D149" t="s">
-        <v>353</v>
+        <v>563</v>
       </c>
       <c r="E149" t="s">
-        <v>618</v>
+        <v>396</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>354</v>
+        <v>188</v>
       </c>
       <c r="H149" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
@@ -5459,10 +4916,10 @@
         <v>30</v>
       </c>
       <c r="D150" t="s">
-        <v>355</v>
+        <v>189</v>
       </c>
       <c r="E150" t="s">
-        <v>619</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5472,20 +4929,17 @@
       <c r="B151" t="s">
         <v>33</v>
       </c>
-      <c r="C151" t="s">
-        <v>356</v>
-      </c>
       <c r="D151" t="s">
-        <v>357</v>
+        <v>564</v>
       </c>
       <c r="E151" t="s">
-        <v>620</v>
+        <v>398</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>358</v>
+        <v>190</v>
       </c>
       <c r="H151" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
@@ -5493,10 +4947,10 @@
         <v>30</v>
       </c>
       <c r="D152" t="s">
-        <v>359</v>
+        <v>191</v>
       </c>
       <c r="E152" t="s">
-        <v>621</v>
+        <v>399</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5506,20 +4960,17 @@
       <c r="B153" t="s">
         <v>33</v>
       </c>
-      <c r="C153" t="s">
-        <v>360</v>
-      </c>
       <c r="D153" t="s">
-        <v>361</v>
+        <v>565</v>
       </c>
       <c r="E153" t="s">
-        <v>622</v>
+        <v>400</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="H153" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5530,19 +4981,19 @@
         <v>33</v>
       </c>
       <c r="C154" t="s">
-        <v>363</v>
+        <v>193</v>
       </c>
       <c r="D154" t="s">
-        <v>364</v>
+        <v>566</v>
       </c>
       <c r="E154" t="s">
-        <v>623</v>
+        <v>401</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>365</v>
+        <v>194</v>
       </c>
       <c r="H154" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
@@ -5550,10 +5001,10 @@
         <v>30</v>
       </c>
       <c r="D155" t="s">
-        <v>366</v>
+        <v>195</v>
       </c>
       <c r="E155" t="s">
-        <v>624</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
@@ -5561,21 +5012,21 @@
         <v>33</v>
       </c>
       <c r="D156" t="s">
-        <v>367</v>
+        <v>196</v>
       </c>
       <c r="E156" t="s">
-        <v>625</v>
+        <v>403</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D157" t="s">
-        <v>368</v>
+        <v>197</v>
       </c>
       <c r="E157" t="s">
-        <v>626</v>
+        <v>404</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5583,22 +5034,19 @@
         <v>32</v>
       </c>
       <c r="B158" t="s">
-        <v>172</v>
-      </c>
-      <c r="C158" t="s">
-        <v>369</v>
+        <v>106</v>
       </c>
       <c r="D158" t="s">
-        <v>370</v>
+        <v>567</v>
       </c>
       <c r="E158" t="s">
-        <v>627</v>
+        <v>405</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>371</v>
+        <v>198</v>
       </c>
       <c r="H158" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5606,33 +5054,30 @@
         <v>32</v>
       </c>
       <c r="B159" t="s">
-        <v>172</v>
-      </c>
-      <c r="C159" t="s">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="D159" t="s">
-        <v>373</v>
+        <v>568</v>
       </c>
       <c r="E159" t="s">
-        <v>628</v>
+        <v>406</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>374</v>
+        <v>199</v>
       </c>
       <c r="H159" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D160" t="s">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="E160" t="s">
-        <v>629</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5640,22 +5085,19 @@
         <v>32</v>
       </c>
       <c r="B161" t="s">
-        <v>172</v>
-      </c>
-      <c r="C161" t="s">
-        <v>376</v>
+        <v>106</v>
       </c>
       <c r="D161" t="s">
-        <v>377</v>
+        <v>569</v>
       </c>
       <c r="E161" t="s">
-        <v>630</v>
+        <v>408</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>378</v>
+        <v>201</v>
       </c>
       <c r="H161" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
@@ -5663,21 +5105,21 @@
         <v>33</v>
       </c>
       <c r="D162" t="s">
-        <v>379</v>
+        <v>202</v>
       </c>
       <c r="E162" t="s">
-        <v>631</v>
+        <v>409</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D163" t="s">
-        <v>380</v>
+        <v>203</v>
       </c>
       <c r="E163" t="s">
-        <v>632</v>
+        <v>410</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5685,33 +5127,30 @@
         <v>32</v>
       </c>
       <c r="B164" t="s">
-        <v>172</v>
-      </c>
-      <c r="C164" t="s">
-        <v>381</v>
+        <v>106</v>
       </c>
       <c r="D164" t="s">
-        <v>382</v>
+        <v>570</v>
       </c>
       <c r="E164" t="s">
-        <v>633</v>
+        <v>411</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>482</v>
+        <v>260</v>
       </c>
       <c r="H164" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D165" t="s">
-        <v>383</v>
+        <v>204</v>
       </c>
       <c r="E165" t="s">
-        <v>634</v>
+        <v>412</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5719,22 +5158,19 @@
         <v>32</v>
       </c>
       <c r="B166" t="s">
-        <v>172</v>
-      </c>
-      <c r="C166" t="s">
-        <v>384</v>
+        <v>106</v>
       </c>
       <c r="D166" t="s">
-        <v>385</v>
+        <v>571</v>
       </c>
       <c r="E166" t="s">
-        <v>635</v>
+        <v>413</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>386</v>
+        <v>205</v>
       </c>
       <c r="H166" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
@@ -5742,10 +5178,10 @@
         <v>33</v>
       </c>
       <c r="D167" t="s">
-        <v>387</v>
+        <v>206</v>
       </c>
       <c r="E167" t="s">
-        <v>636</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5753,22 +5189,19 @@
         <v>32</v>
       </c>
       <c r="B168" t="s">
-        <v>68</v>
-      </c>
-      <c r="C168" t="s">
-        <v>388</v>
+        <v>50</v>
       </c>
       <c r="D168" t="s">
-        <v>389</v>
+        <v>572</v>
       </c>
       <c r="E168" t="s">
-        <v>637</v>
+        <v>415</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>390</v>
+        <v>207</v>
       </c>
       <c r="H168" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
@@ -5776,10 +5209,10 @@
         <v>33</v>
       </c>
       <c r="D169" t="s">
-        <v>391</v>
+        <v>208</v>
       </c>
       <c r="E169" t="s">
-        <v>638</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5787,22 +5220,19 @@
         <v>32</v>
       </c>
       <c r="B170" t="s">
-        <v>68</v>
-      </c>
-      <c r="C170" t="s">
-        <v>392</v>
+        <v>50</v>
       </c>
       <c r="D170" t="s">
-        <v>393</v>
+        <v>573</v>
       </c>
       <c r="E170" t="s">
-        <v>639</v>
+        <v>417</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>394</v>
+        <v>209</v>
       </c>
       <c r="H170" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
@@ -5810,10 +5240,10 @@
         <v>5</v>
       </c>
       <c r="D171" t="s">
-        <v>395</v>
+        <v>210</v>
       </c>
       <c r="E171" t="s">
-        <v>640</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
@@ -5821,10 +5251,10 @@
         <v>30</v>
       </c>
       <c r="D172" t="s">
-        <v>396</v>
+        <v>211</v>
       </c>
       <c r="E172" t="s">
-        <v>641</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5834,20 +5264,17 @@
       <c r="B173" t="s">
         <v>33</v>
       </c>
-      <c r="C173" t="s">
-        <v>397</v>
-      </c>
       <c r="D173" t="s">
-        <v>398</v>
+        <v>574</v>
       </c>
       <c r="E173" t="s">
-        <v>642</v>
+        <v>420</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>399</v>
+        <v>212</v>
       </c>
       <c r="H173" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
@@ -5855,10 +5282,10 @@
         <v>30</v>
       </c>
       <c r="D174" t="s">
-        <v>400</v>
+        <v>213</v>
       </c>
       <c r="E174" t="s">
-        <v>643</v>
+        <v>421</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -5868,20 +5295,17 @@
       <c r="B175" t="s">
         <v>33</v>
       </c>
-      <c r="C175" t="s">
-        <v>401</v>
-      </c>
       <c r="D175" t="s">
-        <v>402</v>
+        <v>575</v>
       </c>
       <c r="E175" t="s">
-        <v>644</v>
+        <v>422</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>483</v>
+        <v>261</v>
       </c>
       <c r="H175" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
@@ -5889,10 +5313,10 @@
         <v>30</v>
       </c>
       <c r="D176" t="s">
-        <v>403</v>
+        <v>214</v>
       </c>
       <c r="E176" t="s">
-        <v>645</v>
+        <v>423</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5902,20 +5326,17 @@
       <c r="B177" t="s">
         <v>33</v>
       </c>
-      <c r="C177" t="s">
-        <v>404</v>
-      </c>
       <c r="D177" t="s">
-        <v>405</v>
+        <v>576</v>
       </c>
       <c r="E177" t="s">
-        <v>646</v>
+        <v>424</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>406</v>
+        <v>215</v>
       </c>
       <c r="H177" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5925,20 +5346,17 @@
       <c r="B178" t="s">
         <v>33</v>
       </c>
-      <c r="C178" t="s">
-        <v>407</v>
-      </c>
       <c r="D178" t="s">
-        <v>408</v>
+        <v>577</v>
       </c>
       <c r="E178" t="s">
-        <v>647</v>
+        <v>425</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>409</v>
+        <v>216</v>
       </c>
       <c r="H178" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5949,19 +5367,19 @@
         <v>33</v>
       </c>
       <c r="C179" t="s">
-        <v>410</v>
+        <v>217</v>
       </c>
       <c r="D179" t="s">
-        <v>411</v>
+        <v>578</v>
       </c>
       <c r="E179" t="s">
-        <v>648</v>
+        <v>426</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>412</v>
+        <v>218</v>
       </c>
       <c r="H179" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
@@ -5969,10 +5387,10 @@
         <v>30</v>
       </c>
       <c r="D180" t="s">
-        <v>413</v>
+        <v>219</v>
       </c>
       <c r="E180" t="s">
-        <v>649</v>
+        <v>427</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5982,20 +5400,17 @@
       <c r="B181" t="s">
         <v>33</v>
       </c>
-      <c r="C181" t="s">
-        <v>414</v>
-      </c>
       <c r="D181" t="s">
-        <v>415</v>
+        <v>579</v>
       </c>
       <c r="E181" t="s">
-        <v>650</v>
+        <v>428</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>416</v>
+        <v>220</v>
       </c>
       <c r="H181" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
@@ -6003,10 +5418,10 @@
         <v>5</v>
       </c>
       <c r="D182" t="s">
-        <v>417</v>
+        <v>221</v>
       </c>
       <c r="E182" t="s">
-        <v>651</v>
+        <v>429</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
@@ -6014,10 +5429,10 @@
         <v>30</v>
       </c>
       <c r="D183" t="s">
-        <v>418</v>
+        <v>222</v>
       </c>
       <c r="E183" t="s">
-        <v>652</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6027,20 +5442,17 @@
       <c r="B184" t="s">
         <v>33</v>
       </c>
-      <c r="C184" t="s">
-        <v>419</v>
-      </c>
       <c r="D184" t="s">
-        <v>420</v>
+        <v>580</v>
       </c>
       <c r="E184" t="s">
-        <v>653</v>
+        <v>431</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>421</v>
+        <v>223</v>
       </c>
       <c r="H184" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -6050,20 +5462,17 @@
       <c r="B185" t="s">
         <v>33</v>
       </c>
-      <c r="C185" t="s">
-        <v>422</v>
-      </c>
       <c r="D185" t="s">
-        <v>423</v>
+        <v>581</v>
       </c>
       <c r="E185" t="s">
-        <v>654</v>
+        <v>432</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="H185" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6073,20 +5482,17 @@
       <c r="B186" t="s">
         <v>33</v>
       </c>
-      <c r="C186" t="s">
-        <v>425</v>
-      </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>582</v>
       </c>
       <c r="E186" t="s">
-        <v>655</v>
+        <v>433</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>427</v>
+        <v>225</v>
       </c>
       <c r="H186" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
@@ -6094,10 +5500,10 @@
         <v>30</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>226</v>
       </c>
       <c r="E187" t="s">
-        <v>656</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6107,20 +5513,17 @@
       <c r="B188" t="s">
         <v>33</v>
       </c>
-      <c r="C188" t="s">
-        <v>429</v>
-      </c>
       <c r="D188" t="s">
-        <v>430</v>
+        <v>583</v>
       </c>
       <c r="E188" t="s">
-        <v>657</v>
+        <v>435</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>431</v>
+        <v>227</v>
       </c>
       <c r="H188" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
@@ -6128,10 +5531,10 @@
         <v>30</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>228</v>
       </c>
       <c r="E189" t="s">
-        <v>658</v>
+        <v>436</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -6139,10 +5542,10 @@
         <v>33</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>229</v>
       </c>
       <c r="E190" t="s">
-        <v>659</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6150,22 +5553,19 @@
         <v>32</v>
       </c>
       <c r="B191" t="s">
-        <v>68</v>
-      </c>
-      <c r="C191" t="s">
-        <v>434</v>
+        <v>50</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>584</v>
       </c>
       <c r="E191" t="s">
-        <v>660</v>
+        <v>438</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>436</v>
+        <v>230</v>
       </c>
       <c r="H191" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
@@ -6173,10 +5573,10 @@
         <v>33</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>231</v>
       </c>
       <c r="E192" t="s">
-        <v>661</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6184,22 +5584,19 @@
         <v>32</v>
       </c>
       <c r="B193" t="s">
-        <v>68</v>
-      </c>
-      <c r="C193" t="s">
-        <v>438</v>
+        <v>50</v>
       </c>
       <c r="D193" t="s">
-        <v>439</v>
+        <v>585</v>
       </c>
       <c r="E193" t="s">
-        <v>662</v>
+        <v>440</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>484</v>
+        <v>262</v>
       </c>
       <c r="H193" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
@@ -6207,10 +5604,10 @@
         <v>30</v>
       </c>
       <c r="D194" t="s">
-        <v>440</v>
+        <v>232</v>
       </c>
       <c r="E194" t="s">
-        <v>663</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6220,20 +5617,17 @@
       <c r="B195" t="s">
         <v>33</v>
       </c>
-      <c r="C195" t="s">
-        <v>441</v>
-      </c>
       <c r="D195" t="s">
+        <v>586</v>
+      </c>
+      <c r="E195" t="s">
         <v>442</v>
       </c>
-      <c r="E195" t="s">
-        <v>664</v>
-      </c>
       <c r="F195" s="1" t="s">
-        <v>443</v>
+        <v>233</v>
       </c>
       <c r="H195" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
@@ -6241,10 +5635,10 @@
         <v>33</v>
       </c>
       <c r="D196" t="s">
-        <v>444</v>
+        <v>234</v>
       </c>
       <c r="E196" t="s">
-        <v>665</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -6252,22 +5646,19 @@
         <v>32</v>
       </c>
       <c r="B197" t="s">
-        <v>68</v>
-      </c>
-      <c r="C197" t="s">
-        <v>445</v>
+        <v>50</v>
       </c>
       <c r="D197" t="s">
-        <v>446</v>
+        <v>587</v>
       </c>
       <c r="E197" t="s">
-        <v>666</v>
+        <v>444</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>447</v>
+        <v>235</v>
       </c>
       <c r="H197" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
@@ -6275,10 +5666,10 @@
         <v>33</v>
       </c>
       <c r="D198" t="s">
-        <v>448</v>
+        <v>236</v>
       </c>
       <c r="E198" t="s">
-        <v>667</v>
+        <v>445</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6286,22 +5677,19 @@
         <v>32</v>
       </c>
       <c r="B199" t="s">
-        <v>68</v>
-      </c>
-      <c r="C199" t="s">
-        <v>449</v>
+        <v>50</v>
       </c>
       <c r="D199" t="s">
-        <v>450</v>
+        <v>588</v>
       </c>
       <c r="E199" t="s">
-        <v>668</v>
+        <v>446</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>451</v>
+        <v>237</v>
       </c>
       <c r="H199" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
@@ -6309,10 +5697,10 @@
         <v>33</v>
       </c>
       <c r="D200" t="s">
-        <v>452</v>
+        <v>238</v>
       </c>
       <c r="E200" t="s">
-        <v>669</v>
+        <v>447</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6320,22 +5708,19 @@
         <v>32</v>
       </c>
       <c r="B201" t="s">
-        <v>68</v>
-      </c>
-      <c r="C201" t="s">
-        <v>453</v>
+        <v>50</v>
       </c>
       <c r="D201" t="s">
-        <v>454</v>
+        <v>589</v>
       </c>
       <c r="E201" t="s">
-        <v>670</v>
+        <v>448</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>455</v>
+        <v>239</v>
       </c>
       <c r="H201" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
@@ -6343,10 +5728,10 @@
         <v>5</v>
       </c>
       <c r="D202" t="s">
-        <v>456</v>
+        <v>240</v>
       </c>
       <c r="E202" t="s">
-        <v>671</v>
+        <v>449</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
@@ -6354,10 +5739,10 @@
         <v>30</v>
       </c>
       <c r="D203" t="s">
-        <v>457</v>
+        <v>241</v>
       </c>
       <c r="E203" t="s">
-        <v>672</v>
+        <v>450</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6367,20 +5752,17 @@
       <c r="B204" t="s">
         <v>33</v>
       </c>
-      <c r="C204" t="s">
-        <v>458</v>
-      </c>
       <c r="D204" t="s">
-        <v>459</v>
+        <v>590</v>
       </c>
       <c r="E204" t="s">
-        <v>673</v>
+        <v>451</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>460</v>
+        <v>242</v>
       </c>
       <c r="H204" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
@@ -6388,10 +5770,10 @@
         <v>30</v>
       </c>
       <c r="D205" t="s">
-        <v>461</v>
+        <v>243</v>
       </c>
       <c r="E205" t="s">
-        <v>674</v>
+        <v>452</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6401,20 +5783,17 @@
       <c r="B206" t="s">
         <v>33</v>
       </c>
-      <c r="C206" t="s">
-        <v>462</v>
-      </c>
       <c r="D206" t="s">
-        <v>463</v>
+        <v>591</v>
       </c>
       <c r="E206" t="s">
-        <v>675</v>
+        <v>453</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>464</v>
+        <v>244</v>
       </c>
       <c r="H206" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
@@ -6422,10 +5801,10 @@
         <v>30</v>
       </c>
       <c r="D207" t="s">
-        <v>465</v>
+        <v>245</v>
       </c>
       <c r="E207" t="s">
-        <v>676</v>
+        <v>454</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
@@ -6435,20 +5814,17 @@
       <c r="B208" t="s">
         <v>33</v>
       </c>
-      <c r="C208" t="s">
-        <v>466</v>
-      </c>
       <c r="D208" t="s">
-        <v>467</v>
+        <v>592</v>
       </c>
       <c r="E208" t="s">
-        <v>677</v>
+        <v>455</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>468</v>
+        <v>246</v>
       </c>
       <c r="H208" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -6510,35 +5886,35 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>678</v>
+        <v>456</v>
       </c>
       <c r="C2" t="s">
-        <v>469</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>679</v>
+        <v>457</v>
       </c>
       <c r="C3" t="s">
-        <v>470</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="B4" t="s">
-        <v>680</v>
+        <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>471</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
